--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FBE4676-770F-4FCD-A18F-306E2D7B1D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9FBD5B-EF3C-47CF-B375-5E9983653D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -203,6 +203,15 @@
   </si>
   <si>
     <t>Extreme humidity</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today I explained a code infront of the class. </t>
   </si>
 </sst>
 </file>
@@ -983,7 +992,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
-        <v>46223</v>
+        <v>46246</v>
       </c>
       <c r="B6" s="9">
         <v>480</v>
@@ -1027,27 +1036,51 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="15" t="str">
+    <row r="7" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="8">
+        <v>46247</v>
+      </c>
+      <c r="B7" s="14">
+        <v>380</v>
+      </c>
+      <c r="C7" s="14">
+        <v>30</v>
+      </c>
+      <c r="D7" s="14">
+        <v>60</v>
+      </c>
+      <c r="E7" s="14">
+        <v>60</v>
+      </c>
+      <c r="F7" s="14">
+        <v>480</v>
+      </c>
+      <c r="G7" s="14">
+        <v>8</v>
+      </c>
+      <c r="H7" s="14">
+        <v>150</v>
+      </c>
+      <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J7" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" s="16"/>
-      <c r="N7" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="13"/>

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9FBD5B-EF3C-47CF-B375-5E9983653D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F879FBE-C4AC-4338-88DF-8950005BC27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -212,6 +212,12 @@
   </si>
   <si>
     <t xml:space="preserve">Today I explained a code infront of the class. </t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It was a good day. </t>
   </si>
 </sst>
 </file>
@@ -1083,26 +1089,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="8">
+        <v>46248</v>
+      </c>
+      <c r="B8" s="14">
+        <v>360</v>
+      </c>
+      <c r="C8" s="14">
+        <v>45</v>
+      </c>
+      <c r="D8" s="14">
+        <v>60</v>
+      </c>
+      <c r="E8" s="14">
+        <v>45</v>
+      </c>
+      <c r="F8" s="14">
+        <v>360</v>
+      </c>
+      <c r="G8" s="14">
+        <v>6</v>
+      </c>
+      <c r="H8" s="14">
+        <v>180</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="13"/>

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F879FBE-C4AC-4338-88DF-8950005BC27A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E125653-AD3C-4424-BB0F-04155F80C4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -218,6 +218,12 @@
   </si>
   <si>
     <t xml:space="preserve">It was a good day. </t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>It was holiday and the day didn't had much activity.</t>
   </si>
 </sst>
 </file>
@@ -1134,27 +1140,51 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+    <row r="9" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="8">
+        <v>46249</v>
+      </c>
+      <c r="B9" s="14">
+        <v>360</v>
+      </c>
+      <c r="C9" s="14">
+        <v>15</v>
+      </c>
+      <c r="D9" s="14">
+        <v>45</v>
+      </c>
+      <c r="E9" s="14">
+        <v>30</v>
+      </c>
+      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0</v>
+      </c>
+      <c r="H9" s="14">
+        <v>440</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>550</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="13"/>

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E125653-AD3C-4424-BB0F-04155F80C4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24CF8FD-68F9-47BF-988E-19F238E698BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,12 @@
   </si>
   <si>
     <t>It was holiday and the day didn't had much activity.</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Unproductive day</t>
   </si>
 </sst>
 </file>
@@ -1187,26 +1193,50 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="8">
+        <v>46250</v>
+      </c>
+      <c r="B10" s="14">
+        <v>380</v>
+      </c>
+      <c r="C10" s="14">
+        <v>10</v>
+      </c>
+      <c r="D10" s="14">
+        <v>60</v>
+      </c>
+      <c r="E10" s="14">
+        <v>30</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>300</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>780</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>660</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="13"/>

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E24CF8FD-68F9-47BF-988E-19F238E698BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEA09D2-8F76-4260-85EB-15D405D9681D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -231,6 +231,15 @@
   <si>
     <t>Unproductive day</t>
   </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today I voluntiered infront of class to speak on any topic from SDGs given by the teacher. </t>
+  </si>
+  <si>
+    <t>Steps</t>
+  </si>
 </sst>
 </file>
 
@@ -368,7 +377,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -412,6 +421,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -880,7 +892,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:O401"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -892,9 +904,10 @@
     <col min="12" max="12" width="15" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="28" customWidth="1"/>
+    <col min="15" max="15" width="19.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="19" t="s">
         <v>29</v>
       </c>
@@ -912,7 +925,7 @@
       <c r="M1" s="19"/>
       <c r="N1" s="19"/>
     </row>
-    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
@@ -929,7 +942,7 @@
       </c>
       <c r="G2" s="20"/>
     </row>
-    <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
@@ -946,7 +959,7 @@
       </c>
       <c r="G3" s="20"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="18" t="s">
         <v>34</v>
       </c>
@@ -964,7 +977,7 @@
       <c r="M4" s="18"/>
       <c r="N4" s="18"/>
     </row>
-    <row r="5" spans="1:14" ht="42" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" ht="42" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -1007,8 +1020,11 @@
       <c r="N5" s="7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O5" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>46246</v>
       </c>
@@ -1053,8 +1069,11 @@
       <c r="N6" s="12" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="O6" s="21">
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="8">
         <v>46247</v>
       </c>
@@ -1099,8 +1118,11 @@
       <c r="N7" s="17" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O7" s="17">
+        <v>8023</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="8">
         <v>46248</v>
       </c>
@@ -1145,8 +1167,11 @@
       <c r="N8" s="17" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="O8" s="17">
+        <v>11206</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>46249</v>
       </c>
@@ -1191,8 +1216,11 @@
       <c r="N9" s="17" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O9" s="17">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>46250</v>
       </c>
@@ -1237,52 +1265,109 @@
       <c r="N10" s="17" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="O10" s="17">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B11" s="14">
+        <v>400</v>
+      </c>
+      <c r="C11" s="14">
+        <v>10</v>
+      </c>
+      <c r="D11" s="14">
+        <v>30</v>
+      </c>
+      <c r="E11" s="14">
+        <v>0</v>
+      </c>
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
+        <v>450</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+        <v>550</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="O11" s="17">
+        <v>5399</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="8">
+        <v>46252</v>
+      </c>
+      <c r="B12" s="14">
+        <v>300</v>
+      </c>
+      <c r="C12" s="14">
+        <v>30</v>
+      </c>
+      <c r="D12" s="14">
+        <v>60</v>
+      </c>
+      <c r="E12" s="14">
+        <v>30</v>
+      </c>
+      <c r="F12" s="14">
+        <v>360</v>
+      </c>
+      <c r="G12" s="14">
+        <v>6</v>
+      </c>
+      <c r="H12" s="14">
+        <v>300</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+        <v>360</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="O12" s="17">
+        <v>10744</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="13"/>
       <c r="B13" s="14"/>
       <c r="C13" s="14"/>
@@ -1303,8 +1388,9 @@
       <c r="L13" s="16"/>
       <c r="M13" s="16"/>
       <c r="N13" s="17"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O13" s="17"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -1325,8 +1411,9 @@
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
       <c r="N14" s="17"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O14" s="17"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="13"/>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -1347,8 +1434,9 @@
       <c r="L15" s="16"/>
       <c r="M15" s="16"/>
       <c r="N15" s="17"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O15" s="17"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
@@ -1369,8 +1457,9 @@
       <c r="L16" s="16"/>
       <c r="M16" s="16"/>
       <c r="N16" s="17"/>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O16" s="17"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="13"/>
       <c r="B17" s="14"/>
       <c r="C17" s="14"/>
@@ -1391,8 +1480,9 @@
       <c r="L17" s="16"/>
       <c r="M17" s="16"/>
       <c r="N17" s="17"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O17" s="17"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="13"/>
       <c r="B18" s="14"/>
       <c r="C18" s="14"/>
@@ -1413,8 +1503,9 @@
       <c r="L18" s="16"/>
       <c r="M18" s="16"/>
       <c r="N18" s="17"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O18" s="17"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="13"/>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -1435,8 +1526,9 @@
       <c r="L19" s="16"/>
       <c r="M19" s="16"/>
       <c r="N19" s="17"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O19" s="17"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>
       <c r="B20" s="14"/>
       <c r="C20" s="14"/>
@@ -1457,8 +1549,9 @@
       <c r="L20" s="16"/>
       <c r="M20" s="16"/>
       <c r="N20" s="17"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O20" s="17"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="13"/>
       <c r="B21" s="14"/>
       <c r="C21" s="14"/>
@@ -1479,8 +1572,9 @@
       <c r="L21" s="16"/>
       <c r="M21" s="16"/>
       <c r="N21" s="17"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O21" s="17"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="13"/>
       <c r="B22" s="14"/>
       <c r="C22" s="14"/>
@@ -1501,8 +1595,9 @@
       <c r="L22" s="16"/>
       <c r="M22" s="16"/>
       <c r="N22" s="17"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O22" s="17"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="13"/>
       <c r="B23" s="14"/>
       <c r="C23" s="14"/>
@@ -1523,8 +1618,9 @@
       <c r="L23" s="16"/>
       <c r="M23" s="16"/>
       <c r="N23" s="17"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O23" s="17"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="13"/>
       <c r="B24" s="14"/>
       <c r="C24" s="14"/>
@@ -1545,8 +1641,9 @@
       <c r="L24" s="16"/>
       <c r="M24" s="16"/>
       <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O24" s="17"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="13"/>
       <c r="B25" s="14"/>
       <c r="C25" s="14"/>
@@ -1567,8 +1664,9 @@
       <c r="L25" s="16"/>
       <c r="M25" s="16"/>
       <c r="N25" s="17"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O25" s="17"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="13"/>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -1589,8 +1687,9 @@
       <c r="L26" s="16"/>
       <c r="M26" s="16"/>
       <c r="N26" s="17"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O26" s="17"/>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="13"/>
       <c r="B27" s="14"/>
       <c r="C27" s="14"/>
@@ -1611,8 +1710,9 @@
       <c r="L27" s="16"/>
       <c r="M27" s="16"/>
       <c r="N27" s="17"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O27" s="17"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" s="13"/>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
@@ -1633,8 +1733,9 @@
       <c r="L28" s="16"/>
       <c r="M28" s="16"/>
       <c r="N28" s="17"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O28" s="17"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" s="13"/>
       <c r="B29" s="14"/>
       <c r="C29" s="14"/>
@@ -1655,8 +1756,9 @@
       <c r="L29" s="16"/>
       <c r="M29" s="16"/>
       <c r="N29" s="17"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O29" s="17"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="13"/>
       <c r="B30" s="14"/>
       <c r="C30" s="14"/>
@@ -1677,8 +1779,9 @@
       <c r="L30" s="16"/>
       <c r="M30" s="16"/>
       <c r="N30" s="17"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O30" s="17"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="13"/>
       <c r="B31" s="14"/>
       <c r="C31" s="14"/>
@@ -1699,8 +1802,9 @@
       <c r="L31" s="16"/>
       <c r="M31" s="16"/>
       <c r="N31" s="17"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O31" s="17"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" s="13"/>
       <c r="B32" s="14"/>
       <c r="C32" s="14"/>
@@ -1721,8 +1825,9 @@
       <c r="L32" s="16"/>
       <c r="M32" s="16"/>
       <c r="N32" s="17"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O32" s="17"/>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="13"/>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -1743,8 +1848,9 @@
       <c r="L33" s="16"/>
       <c r="M33" s="16"/>
       <c r="N33" s="17"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O33" s="17"/>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="13"/>
       <c r="B34" s="14"/>
       <c r="C34" s="14"/>
@@ -1765,8 +1871,9 @@
       <c r="L34" s="16"/>
       <c r="M34" s="16"/>
       <c r="N34" s="17"/>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O34" s="17"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="13"/>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
@@ -1787,8 +1894,9 @@
       <c r="L35" s="16"/>
       <c r="M35" s="16"/>
       <c r="N35" s="17"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O35" s="17"/>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" s="13"/>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
@@ -1809,8 +1917,9 @@
       <c r="L36" s="16"/>
       <c r="M36" s="16"/>
       <c r="N36" s="17"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O36" s="17"/>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="13"/>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
@@ -1831,8 +1940,9 @@
       <c r="L37" s="16"/>
       <c r="M37" s="16"/>
       <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O37" s="17"/>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="13"/>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
@@ -1853,8 +1963,9 @@
       <c r="L38" s="16"/>
       <c r="M38" s="16"/>
       <c r="N38" s="17"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O38" s="17"/>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" s="13"/>
       <c r="B39" s="14"/>
       <c r="C39" s="14"/>
@@ -1875,8 +1986,9 @@
       <c r="L39" s="16"/>
       <c r="M39" s="16"/>
       <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O39" s="17"/>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="13"/>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
@@ -1897,8 +2009,9 @@
       <c r="L40" s="16"/>
       <c r="M40" s="16"/>
       <c r="N40" s="17"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O40" s="17"/>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" s="13"/>
       <c r="B41" s="14"/>
       <c r="C41" s="14"/>
@@ -1919,8 +2032,9 @@
       <c r="L41" s="16"/>
       <c r="M41" s="16"/>
       <c r="N41" s="17"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O41" s="17"/>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="13"/>
       <c r="B42" s="14"/>
       <c r="C42" s="14"/>
@@ -1941,8 +2055,9 @@
       <c r="L42" s="16"/>
       <c r="M42" s="16"/>
       <c r="N42" s="17"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O42" s="17"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="13"/>
       <c r="B43" s="14"/>
       <c r="C43" s="14"/>
@@ -1963,8 +2078,9 @@
       <c r="L43" s="16"/>
       <c r="M43" s="16"/>
       <c r="N43" s="17"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O43" s="17"/>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" s="13"/>
       <c r="B44" s="14"/>
       <c r="C44" s="14"/>
@@ -1985,8 +2101,9 @@
       <c r="L44" s="16"/>
       <c r="M44" s="16"/>
       <c r="N44" s="17"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O44" s="17"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="13"/>
       <c r="B45" s="14"/>
       <c r="C45" s="14"/>
@@ -2007,8 +2124,9 @@
       <c r="L45" s="16"/>
       <c r="M45" s="16"/>
       <c r="N45" s="17"/>
-    </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O45" s="17"/>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="13"/>
       <c r="B46" s="14"/>
       <c r="C46" s="14"/>
@@ -2029,8 +2147,9 @@
       <c r="L46" s="16"/>
       <c r="M46" s="16"/>
       <c r="N46" s="17"/>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O46" s="17"/>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="13"/>
       <c r="B47" s="14"/>
       <c r="C47" s="14"/>
@@ -2051,8 +2170,9 @@
       <c r="L47" s="16"/>
       <c r="M47" s="16"/>
       <c r="N47" s="17"/>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O47" s="17"/>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="13"/>
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
@@ -2073,8 +2193,9 @@
       <c r="L48" s="16"/>
       <c r="M48" s="16"/>
       <c r="N48" s="17"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O48" s="17"/>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="13"/>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
@@ -2095,8 +2216,9 @@
       <c r="L49" s="16"/>
       <c r="M49" s="16"/>
       <c r="N49" s="17"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O49" s="17"/>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" s="13"/>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
@@ -2117,8 +2239,9 @@
       <c r="L50" s="16"/>
       <c r="M50" s="16"/>
       <c r="N50" s="17"/>
-    </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O50" s="17"/>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" s="13"/>
       <c r="B51" s="14"/>
       <c r="C51" s="14"/>
@@ -2139,8 +2262,9 @@
       <c r="L51" s="16"/>
       <c r="M51" s="16"/>
       <c r="N51" s="17"/>
-    </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O51" s="17"/>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" s="13"/>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
@@ -2161,8 +2285,9 @@
       <c r="L52" s="16"/>
       <c r="M52" s="16"/>
       <c r="N52" s="17"/>
-    </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O52" s="17"/>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" s="13"/>
       <c r="B53" s="14"/>
       <c r="C53" s="14"/>
@@ -2183,8 +2308,9 @@
       <c r="L53" s="16"/>
       <c r="M53" s="16"/>
       <c r="N53" s="17"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O53" s="17"/>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" s="13"/>
       <c r="B54" s="14"/>
       <c r="C54" s="14"/>
@@ -2205,8 +2331,9 @@
       <c r="L54" s="16"/>
       <c r="M54" s="16"/>
       <c r="N54" s="17"/>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O54" s="17"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" s="13"/>
       <c r="B55" s="14"/>
       <c r="C55" s="14"/>
@@ -2227,8 +2354,9 @@
       <c r="L55" s="16"/>
       <c r="M55" s="16"/>
       <c r="N55" s="17"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O55" s="17"/>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" s="13"/>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
@@ -2249,8 +2377,9 @@
       <c r="L56" s="16"/>
       <c r="M56" s="16"/>
       <c r="N56" s="17"/>
-    </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O56" s="17"/>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" s="13"/>
       <c r="B57" s="14"/>
       <c r="C57" s="14"/>
@@ -2271,8 +2400,9 @@
       <c r="L57" s="16"/>
       <c r="M57" s="16"/>
       <c r="N57" s="17"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O57" s="17"/>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" s="13"/>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -2293,8 +2423,9 @@
       <c r="L58" s="16"/>
       <c r="M58" s="16"/>
       <c r="N58" s="17"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O58" s="17"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" s="13"/>
       <c r="B59" s="14"/>
       <c r="C59" s="14"/>
@@ -2315,8 +2446,9 @@
       <c r="L59" s="16"/>
       <c r="M59" s="16"/>
       <c r="N59" s="17"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O59" s="17"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" s="13"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
@@ -2337,8 +2469,9 @@
       <c r="L60" s="16"/>
       <c r="M60" s="16"/>
       <c r="N60" s="17"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O60" s="17"/>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" s="13"/>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
@@ -2359,8 +2492,9 @@
       <c r="L61" s="16"/>
       <c r="M61" s="16"/>
       <c r="N61" s="17"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O61" s="17"/>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" s="13"/>
       <c r="B62" s="14"/>
       <c r="C62" s="14"/>
@@ -2381,8 +2515,9 @@
       <c r="L62" s="16"/>
       <c r="M62" s="16"/>
       <c r="N62" s="17"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O62" s="17"/>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" s="13"/>
       <c r="B63" s="14"/>
       <c r="C63" s="14"/>
@@ -2403,8 +2538,9 @@
       <c r="L63" s="16"/>
       <c r="M63" s="16"/>
       <c r="N63" s="17"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O63" s="17"/>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" s="13"/>
       <c r="B64" s="14"/>
       <c r="C64" s="14"/>
@@ -2425,8 +2561,9 @@
       <c r="L64" s="16"/>
       <c r="M64" s="16"/>
       <c r="N64" s="17"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O64" s="17"/>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" s="13"/>
       <c r="B65" s="14"/>
       <c r="C65" s="14"/>
@@ -2447,8 +2584,9 @@
       <c r="L65" s="16"/>
       <c r="M65" s="16"/>
       <c r="N65" s="17"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O65" s="17"/>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" s="13"/>
       <c r="B66" s="14"/>
       <c r="C66" s="14"/>
@@ -2469,8 +2607,9 @@
       <c r="L66" s="16"/>
       <c r="M66" s="16"/>
       <c r="N66" s="17"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O66" s="17"/>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" s="13"/>
       <c r="B67" s="14"/>
       <c r="C67" s="14"/>
@@ -2491,8 +2630,9 @@
       <c r="L67" s="16"/>
       <c r="M67" s="16"/>
       <c r="N67" s="17"/>
-    </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O67" s="17"/>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" s="13"/>
       <c r="B68" s="14"/>
       <c r="C68" s="14"/>
@@ -2513,8 +2653,9 @@
       <c r="L68" s="16"/>
       <c r="M68" s="16"/>
       <c r="N68" s="17"/>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O68" s="17"/>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" s="13"/>
       <c r="B69" s="14"/>
       <c r="C69" s="14"/>
@@ -2535,8 +2676,9 @@
       <c r="L69" s="16"/>
       <c r="M69" s="16"/>
       <c r="N69" s="17"/>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O69" s="17"/>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" s="13"/>
       <c r="B70" s="14"/>
       <c r="C70" s="14"/>
@@ -2557,8 +2699,9 @@
       <c r="L70" s="16"/>
       <c r="M70" s="16"/>
       <c r="N70" s="17"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O70" s="17"/>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" s="13"/>
       <c r="B71" s="14"/>
       <c r="C71" s="14"/>
@@ -2579,8 +2722,9 @@
       <c r="L71" s="16"/>
       <c r="M71" s="16"/>
       <c r="N71" s="17"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O71" s="17"/>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" s="13"/>
       <c r="B72" s="14"/>
       <c r="C72" s="14"/>
@@ -2601,8 +2745,9 @@
       <c r="L72" s="16"/>
       <c r="M72" s="16"/>
       <c r="N72" s="17"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O72" s="17"/>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" s="13"/>
       <c r="B73" s="14"/>
       <c r="C73" s="14"/>
@@ -2623,8 +2768,9 @@
       <c r="L73" s="16"/>
       <c r="M73" s="16"/>
       <c r="N73" s="17"/>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O73" s="17"/>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" s="13"/>
       <c r="B74" s="14"/>
       <c r="C74" s="14"/>
@@ -2645,8 +2791,9 @@
       <c r="L74" s="16"/>
       <c r="M74" s="16"/>
       <c r="N74" s="17"/>
-    </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O74" s="17"/>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" s="13"/>
       <c r="B75" s="14"/>
       <c r="C75" s="14"/>
@@ -2667,8 +2814,9 @@
       <c r="L75" s="16"/>
       <c r="M75" s="16"/>
       <c r="N75" s="17"/>
-    </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O75" s="17"/>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" s="13"/>
       <c r="B76" s="14"/>
       <c r="C76" s="14"/>
@@ -2689,8 +2837,9 @@
       <c r="L76" s="16"/>
       <c r="M76" s="16"/>
       <c r="N76" s="17"/>
-    </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O76" s="17"/>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" s="13"/>
       <c r="B77" s="14"/>
       <c r="C77" s="14"/>
@@ -2711,8 +2860,9 @@
       <c r="L77" s="16"/>
       <c r="M77" s="16"/>
       <c r="N77" s="17"/>
-    </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O77" s="17"/>
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" s="13"/>
       <c r="B78" s="14"/>
       <c r="C78" s="14"/>
@@ -2733,8 +2883,9 @@
       <c r="L78" s="16"/>
       <c r="M78" s="16"/>
       <c r="N78" s="17"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O78" s="17"/>
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" s="13"/>
       <c r="B79" s="14"/>
       <c r="C79" s="14"/>
@@ -2755,8 +2906,9 @@
       <c r="L79" s="16"/>
       <c r="M79" s="16"/>
       <c r="N79" s="17"/>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O79" s="17"/>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" s="13"/>
       <c r="B80" s="14"/>
       <c r="C80" s="14"/>
@@ -2777,8 +2929,9 @@
       <c r="L80" s="16"/>
       <c r="M80" s="16"/>
       <c r="N80" s="17"/>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O80" s="17"/>
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" s="13"/>
       <c r="B81" s="14"/>
       <c r="C81" s="14"/>
@@ -2799,8 +2952,9 @@
       <c r="L81" s="16"/>
       <c r="M81" s="16"/>
       <c r="N81" s="17"/>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O81" s="17"/>
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" s="13"/>
       <c r="B82" s="14"/>
       <c r="C82" s="14"/>
@@ -2821,8 +2975,9 @@
       <c r="L82" s="16"/>
       <c r="M82" s="16"/>
       <c r="N82" s="17"/>
-    </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O82" s="17"/>
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" s="13"/>
       <c r="B83" s="14"/>
       <c r="C83" s="14"/>
@@ -2843,8 +2998,9 @@
       <c r="L83" s="16"/>
       <c r="M83" s="16"/>
       <c r="N83" s="17"/>
-    </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O83" s="17"/>
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" s="13"/>
       <c r="B84" s="14"/>
       <c r="C84" s="14"/>
@@ -2865,8 +3021,9 @@
       <c r="L84" s="16"/>
       <c r="M84" s="16"/>
       <c r="N84" s="17"/>
-    </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O84" s="17"/>
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" s="13"/>
       <c r="B85" s="14"/>
       <c r="C85" s="14"/>
@@ -2887,8 +3044,9 @@
       <c r="L85" s="16"/>
       <c r="M85" s="16"/>
       <c r="N85" s="17"/>
-    </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O85" s="17"/>
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86" s="13"/>
       <c r="B86" s="14"/>
       <c r="C86" s="14"/>
@@ -2909,8 +3067,9 @@
       <c r="L86" s="16"/>
       <c r="M86" s="16"/>
       <c r="N86" s="17"/>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O86" s="17"/>
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A87" s="13"/>
       <c r="B87" s="14"/>
       <c r="C87" s="14"/>
@@ -2931,8 +3090,9 @@
       <c r="L87" s="16"/>
       <c r="M87" s="16"/>
       <c r="N87" s="17"/>
-    </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O87" s="17"/>
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" s="13"/>
       <c r="B88" s="14"/>
       <c r="C88" s="14"/>
@@ -2953,8 +3113,9 @@
       <c r="L88" s="16"/>
       <c r="M88" s="16"/>
       <c r="N88" s="17"/>
-    </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O88" s="17"/>
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89" s="13"/>
       <c r="B89" s="14"/>
       <c r="C89" s="14"/>
@@ -2975,8 +3136,9 @@
       <c r="L89" s="16"/>
       <c r="M89" s="16"/>
       <c r="N89" s="17"/>
-    </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O89" s="17"/>
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" s="13"/>
       <c r="B90" s="14"/>
       <c r="C90" s="14"/>
@@ -2997,8 +3159,9 @@
       <c r="L90" s="16"/>
       <c r="M90" s="16"/>
       <c r="N90" s="17"/>
-    </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O90" s="17"/>
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" s="13"/>
       <c r="B91" s="14"/>
       <c r="C91" s="14"/>
@@ -3019,8 +3182,9 @@
       <c r="L91" s="16"/>
       <c r="M91" s="16"/>
       <c r="N91" s="17"/>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O91" s="17"/>
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92" s="13"/>
       <c r="B92" s="14"/>
       <c r="C92" s="14"/>
@@ -3041,8 +3205,9 @@
       <c r="L92" s="16"/>
       <c r="M92" s="16"/>
       <c r="N92" s="17"/>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O92" s="17"/>
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" s="13"/>
       <c r="B93" s="14"/>
       <c r="C93" s="14"/>
@@ -3063,8 +3228,9 @@
       <c r="L93" s="16"/>
       <c r="M93" s="16"/>
       <c r="N93" s="17"/>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O93" s="17"/>
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A94" s="13"/>
       <c r="B94" s="14"/>
       <c r="C94" s="14"/>
@@ -3085,8 +3251,9 @@
       <c r="L94" s="16"/>
       <c r="M94" s="16"/>
       <c r="N94" s="17"/>
-    </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O94" s="17"/>
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95" s="13"/>
       <c r="B95" s="14"/>
       <c r="C95" s="14"/>
@@ -3107,8 +3274,9 @@
       <c r="L95" s="16"/>
       <c r="M95" s="16"/>
       <c r="N95" s="17"/>
-    </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O95" s="17"/>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A96" s="13"/>
       <c r="B96" s="14"/>
       <c r="C96" s="14"/>
@@ -3129,8 +3297,9 @@
       <c r="L96" s="16"/>
       <c r="M96" s="16"/>
       <c r="N96" s="17"/>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O96" s="17"/>
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A97" s="13"/>
       <c r="B97" s="14"/>
       <c r="C97" s="14"/>
@@ -3151,8 +3320,9 @@
       <c r="L97" s="16"/>
       <c r="M97" s="16"/>
       <c r="N97" s="17"/>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O97" s="17"/>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A98" s="13"/>
       <c r="B98" s="14"/>
       <c r="C98" s="14"/>
@@ -3173,8 +3343,9 @@
       <c r="L98" s="16"/>
       <c r="M98" s="16"/>
       <c r="N98" s="17"/>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O98" s="17"/>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A99" s="13"/>
       <c r="B99" s="14"/>
       <c r="C99" s="14"/>
@@ -3195,8 +3366,9 @@
       <c r="L99" s="16"/>
       <c r="M99" s="16"/>
       <c r="N99" s="17"/>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O99" s="17"/>
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A100" s="13"/>
       <c r="B100" s="14"/>
       <c r="C100" s="14"/>
@@ -3217,8 +3389,9 @@
       <c r="L100" s="16"/>
       <c r="M100" s="16"/>
       <c r="N100" s="17"/>
-    </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O100" s="17"/>
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A101" s="13"/>
       <c r="B101" s="14"/>
       <c r="C101" s="14"/>
@@ -3239,8 +3412,9 @@
       <c r="L101" s="16"/>
       <c r="M101" s="16"/>
       <c r="N101" s="17"/>
-    </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O101" s="17"/>
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A102" s="13"/>
       <c r="B102" s="14"/>
       <c r="C102" s="14"/>
@@ -3261,8 +3435,9 @@
       <c r="L102" s="16"/>
       <c r="M102" s="16"/>
       <c r="N102" s="17"/>
-    </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O102" s="17"/>
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A103" s="13"/>
       <c r="B103" s="14"/>
       <c r="C103" s="14"/>
@@ -3283,8 +3458,9 @@
       <c r="L103" s="16"/>
       <c r="M103" s="16"/>
       <c r="N103" s="17"/>
-    </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O103" s="17"/>
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A104" s="13"/>
       <c r="B104" s="14"/>
       <c r="C104" s="14"/>
@@ -3305,8 +3481,9 @@
       <c r="L104" s="16"/>
       <c r="M104" s="16"/>
       <c r="N104" s="17"/>
-    </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O104" s="17"/>
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A105" s="13"/>
       <c r="B105" s="14"/>
       <c r="C105" s="14"/>
@@ -3327,8 +3504,9 @@
       <c r="L105" s="16"/>
       <c r="M105" s="16"/>
       <c r="N105" s="17"/>
-    </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O105" s="17"/>
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A106" s="13"/>
       <c r="B106" s="14"/>
       <c r="C106" s="14"/>
@@ -3349,8 +3527,9 @@
       <c r="L106" s="16"/>
       <c r="M106" s="16"/>
       <c r="N106" s="17"/>
-    </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O106" s="17"/>
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A107" s="13"/>
       <c r="B107" s="14"/>
       <c r="C107" s="14"/>
@@ -3371,8 +3550,9 @@
       <c r="L107" s="16"/>
       <c r="M107" s="16"/>
       <c r="N107" s="17"/>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O107" s="17"/>
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A108" s="13"/>
       <c r="B108" s="14"/>
       <c r="C108" s="14"/>
@@ -3393,8 +3573,9 @@
       <c r="L108" s="16"/>
       <c r="M108" s="16"/>
       <c r="N108" s="17"/>
-    </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O108" s="17"/>
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A109" s="13"/>
       <c r="B109" s="14"/>
       <c r="C109" s="14"/>
@@ -3415,8 +3596,9 @@
       <c r="L109" s="16"/>
       <c r="M109" s="16"/>
       <c r="N109" s="17"/>
-    </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O109" s="17"/>
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A110" s="13"/>
       <c r="B110" s="14"/>
       <c r="C110" s="14"/>
@@ -3437,8 +3619,9 @@
       <c r="L110" s="16"/>
       <c r="M110" s="16"/>
       <c r="N110" s="17"/>
-    </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O110" s="17"/>
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A111" s="13"/>
       <c r="B111" s="14"/>
       <c r="C111" s="14"/>
@@ -3459,8 +3642,9 @@
       <c r="L111" s="16"/>
       <c r="M111" s="16"/>
       <c r="N111" s="17"/>
-    </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O111" s="17"/>
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A112" s="13"/>
       <c r="B112" s="14"/>
       <c r="C112" s="14"/>
@@ -3481,8 +3665,9 @@
       <c r="L112" s="16"/>
       <c r="M112" s="16"/>
       <c r="N112" s="17"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O112" s="17"/>
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A113" s="13"/>
       <c r="B113" s="14"/>
       <c r="C113" s="14"/>
@@ -3503,8 +3688,9 @@
       <c r="L113" s="16"/>
       <c r="M113" s="16"/>
       <c r="N113" s="17"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O113" s="17"/>
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A114" s="13"/>
       <c r="B114" s="14"/>
       <c r="C114" s="14"/>
@@ -3525,8 +3711,9 @@
       <c r="L114" s="16"/>
       <c r="M114" s="16"/>
       <c r="N114" s="17"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O114" s="17"/>
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A115" s="13"/>
       <c r="B115" s="14"/>
       <c r="C115" s="14"/>
@@ -3547,8 +3734,9 @@
       <c r="L115" s="16"/>
       <c r="M115" s="16"/>
       <c r="N115" s="17"/>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O115" s="17"/>
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A116" s="13"/>
       <c r="B116" s="14"/>
       <c r="C116" s="14"/>
@@ -3569,8 +3757,9 @@
       <c r="L116" s="16"/>
       <c r="M116" s="16"/>
       <c r="N116" s="17"/>
-    </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O116" s="17"/>
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A117" s="13"/>
       <c r="B117" s="14"/>
       <c r="C117" s="14"/>
@@ -3591,8 +3780,9 @@
       <c r="L117" s="16"/>
       <c r="M117" s="16"/>
       <c r="N117" s="17"/>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O117" s="17"/>
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A118" s="13"/>
       <c r="B118" s="14"/>
       <c r="C118" s="14"/>
@@ -3613,8 +3803,9 @@
       <c r="L118" s="16"/>
       <c r="M118" s="16"/>
       <c r="N118" s="17"/>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O118" s="17"/>
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A119" s="13"/>
       <c r="B119" s="14"/>
       <c r="C119" s="14"/>
@@ -3635,8 +3826,9 @@
       <c r="L119" s="16"/>
       <c r="M119" s="16"/>
       <c r="N119" s="17"/>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O119" s="17"/>
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A120" s="13"/>
       <c r="B120" s="14"/>
       <c r="C120" s="14"/>
@@ -3657,8 +3849,9 @@
       <c r="L120" s="16"/>
       <c r="M120" s="16"/>
       <c r="N120" s="17"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O120" s="17"/>
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A121" s="13"/>
       <c r="B121" s="14"/>
       <c r="C121" s="14"/>
@@ -3679,8 +3872,9 @@
       <c r="L121" s="16"/>
       <c r="M121" s="16"/>
       <c r="N121" s="17"/>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O121" s="17"/>
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A122" s="13"/>
       <c r="B122" s="14"/>
       <c r="C122" s="14"/>
@@ -3701,8 +3895,9 @@
       <c r="L122" s="16"/>
       <c r="M122" s="16"/>
       <c r="N122" s="17"/>
-    </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O122" s="17"/>
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A123" s="13"/>
       <c r="B123" s="14"/>
       <c r="C123" s="14"/>
@@ -3723,8 +3918,9 @@
       <c r="L123" s="16"/>
       <c r="M123" s="16"/>
       <c r="N123" s="17"/>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O123" s="17"/>
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A124" s="13"/>
       <c r="B124" s="14"/>
       <c r="C124" s="14"/>
@@ -3745,8 +3941,9 @@
       <c r="L124" s="16"/>
       <c r="M124" s="16"/>
       <c r="N124" s="17"/>
-    </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O124" s="17"/>
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A125" s="13"/>
       <c r="B125" s="14"/>
       <c r="C125" s="14"/>
@@ -3767,8 +3964,9 @@
       <c r="L125" s="16"/>
       <c r="M125" s="16"/>
       <c r="N125" s="17"/>
-    </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O125" s="17"/>
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A126" s="13"/>
       <c r="B126" s="14"/>
       <c r="C126" s="14"/>
@@ -3789,8 +3987,9 @@
       <c r="L126" s="16"/>
       <c r="M126" s="16"/>
       <c r="N126" s="17"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O126" s="17"/>
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A127" s="13"/>
       <c r="B127" s="14"/>
       <c r="C127" s="14"/>
@@ -3811,8 +4010,9 @@
       <c r="L127" s="16"/>
       <c r="M127" s="16"/>
       <c r="N127" s="17"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O127" s="17"/>
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A128" s="13"/>
       <c r="B128" s="14"/>
       <c r="C128" s="14"/>
@@ -3833,8 +4033,9 @@
       <c r="L128" s="16"/>
       <c r="M128" s="16"/>
       <c r="N128" s="17"/>
-    </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O128" s="17"/>
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A129" s="13"/>
       <c r="B129" s="14"/>
       <c r="C129" s="14"/>
@@ -3855,8 +4056,9 @@
       <c r="L129" s="16"/>
       <c r="M129" s="16"/>
       <c r="N129" s="17"/>
-    </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O129" s="17"/>
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A130" s="13"/>
       <c r="B130" s="14"/>
       <c r="C130" s="14"/>
@@ -3877,8 +4079,9 @@
       <c r="L130" s="16"/>
       <c r="M130" s="16"/>
       <c r="N130" s="17"/>
-    </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O130" s="17"/>
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A131" s="13"/>
       <c r="B131" s="14"/>
       <c r="C131" s="14"/>
@@ -3899,8 +4102,9 @@
       <c r="L131" s="16"/>
       <c r="M131" s="16"/>
       <c r="N131" s="17"/>
-    </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O131" s="17"/>
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A132" s="13"/>
       <c r="B132" s="14"/>
       <c r="C132" s="14"/>
@@ -3921,8 +4125,9 @@
       <c r="L132" s="16"/>
       <c r="M132" s="16"/>
       <c r="N132" s="17"/>
-    </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O132" s="17"/>
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A133" s="13"/>
       <c r="B133" s="14"/>
       <c r="C133" s="14"/>
@@ -3943,8 +4148,9 @@
       <c r="L133" s="16"/>
       <c r="M133" s="16"/>
       <c r="N133" s="17"/>
-    </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O133" s="17"/>
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A134" s="13"/>
       <c r="B134" s="14"/>
       <c r="C134" s="14"/>
@@ -3965,8 +4171,9 @@
       <c r="L134" s="16"/>
       <c r="M134" s="16"/>
       <c r="N134" s="17"/>
-    </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O134" s="17"/>
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A135" s="13"/>
       <c r="B135" s="14"/>
       <c r="C135" s="14"/>
@@ -3987,8 +4194,9 @@
       <c r="L135" s="16"/>
       <c r="M135" s="16"/>
       <c r="N135" s="17"/>
-    </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O135" s="17"/>
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A136" s="13"/>
       <c r="B136" s="14"/>
       <c r="C136" s="14"/>
@@ -4009,8 +4217,9 @@
       <c r="L136" s="16"/>
       <c r="M136" s="16"/>
       <c r="N136" s="17"/>
-    </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O136" s="17"/>
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A137" s="13"/>
       <c r="B137" s="14"/>
       <c r="C137" s="14"/>
@@ -4031,8 +4240,9 @@
       <c r="L137" s="16"/>
       <c r="M137" s="16"/>
       <c r="N137" s="17"/>
-    </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O137" s="17"/>
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A138" s="13"/>
       <c r="B138" s="14"/>
       <c r="C138" s="14"/>
@@ -4053,8 +4263,9 @@
       <c r="L138" s="16"/>
       <c r="M138" s="16"/>
       <c r="N138" s="17"/>
-    </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O138" s="17"/>
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A139" s="13"/>
       <c r="B139" s="14"/>
       <c r="C139" s="14"/>
@@ -4075,8 +4286,9 @@
       <c r="L139" s="16"/>
       <c r="M139" s="16"/>
       <c r="N139" s="17"/>
-    </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O139" s="17"/>
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A140" s="13"/>
       <c r="B140" s="14"/>
       <c r="C140" s="14"/>
@@ -4097,8 +4309,9 @@
       <c r="L140" s="16"/>
       <c r="M140" s="16"/>
       <c r="N140" s="17"/>
-    </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O140" s="17"/>
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A141" s="13"/>
       <c r="B141" s="14"/>
       <c r="C141" s="14"/>
@@ -4119,8 +4332,9 @@
       <c r="L141" s="16"/>
       <c r="M141" s="16"/>
       <c r="N141" s="17"/>
-    </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O141" s="17"/>
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A142" s="13"/>
       <c r="B142" s="14"/>
       <c r="C142" s="14"/>
@@ -4141,8 +4355,9 @@
       <c r="L142" s="16"/>
       <c r="M142" s="16"/>
       <c r="N142" s="17"/>
-    </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O142" s="17"/>
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A143" s="13"/>
       <c r="B143" s="14"/>
       <c r="C143" s="14"/>
@@ -4163,8 +4378,9 @@
       <c r="L143" s="16"/>
       <c r="M143" s="16"/>
       <c r="N143" s="17"/>
-    </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O143" s="17"/>
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A144" s="13"/>
       <c r="B144" s="14"/>
       <c r="C144" s="14"/>
@@ -4185,8 +4401,9 @@
       <c r="L144" s="16"/>
       <c r="M144" s="16"/>
       <c r="N144" s="17"/>
-    </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O144" s="17"/>
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A145" s="13"/>
       <c r="B145" s="14"/>
       <c r="C145" s="14"/>
@@ -4207,8 +4424,9 @@
       <c r="L145" s="16"/>
       <c r="M145" s="16"/>
       <c r="N145" s="17"/>
-    </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O145" s="17"/>
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A146" s="13"/>
       <c r="B146" s="14"/>
       <c r="C146" s="14"/>
@@ -4229,8 +4447,9 @@
       <c r="L146" s="16"/>
       <c r="M146" s="16"/>
       <c r="N146" s="17"/>
-    </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O146" s="17"/>
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A147" s="13"/>
       <c r="B147" s="14"/>
       <c r="C147" s="14"/>
@@ -4251,8 +4470,9 @@
       <c r="L147" s="16"/>
       <c r="M147" s="16"/>
       <c r="N147" s="17"/>
-    </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O147" s="17"/>
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A148" s="13"/>
       <c r="B148" s="14"/>
       <c r="C148" s="14"/>
@@ -4273,8 +4493,9 @@
       <c r="L148" s="16"/>
       <c r="M148" s="16"/>
       <c r="N148" s="17"/>
-    </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O148" s="17"/>
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A149" s="13"/>
       <c r="B149" s="14"/>
       <c r="C149" s="14"/>
@@ -4295,8 +4516,9 @@
       <c r="L149" s="16"/>
       <c r="M149" s="16"/>
       <c r="N149" s="17"/>
-    </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O149" s="17"/>
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A150" s="13"/>
       <c r="B150" s="14"/>
       <c r="C150" s="14"/>
@@ -4317,8 +4539,9 @@
       <c r="L150" s="16"/>
       <c r="M150" s="16"/>
       <c r="N150" s="17"/>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O150" s="17"/>
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A151" s="13"/>
       <c r="B151" s="14"/>
       <c r="C151" s="14"/>
@@ -4339,8 +4562,9 @@
       <c r="L151" s="16"/>
       <c r="M151" s="16"/>
       <c r="N151" s="17"/>
-    </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O151" s="17"/>
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A152" s="13"/>
       <c r="B152" s="14"/>
       <c r="C152" s="14"/>
@@ -4361,8 +4585,9 @@
       <c r="L152" s="16"/>
       <c r="M152" s="16"/>
       <c r="N152" s="17"/>
-    </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O152" s="17"/>
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A153" s="13"/>
       <c r="B153" s="14"/>
       <c r="C153" s="14"/>
@@ -4383,8 +4608,9 @@
       <c r="L153" s="16"/>
       <c r="M153" s="16"/>
       <c r="N153" s="17"/>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O153" s="17"/>
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A154" s="13"/>
       <c r="B154" s="14"/>
       <c r="C154" s="14"/>
@@ -4405,8 +4631,9 @@
       <c r="L154" s="16"/>
       <c r="M154" s="16"/>
       <c r="N154" s="17"/>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O154" s="17"/>
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A155" s="13"/>
       <c r="B155" s="14"/>
       <c r="C155" s="14"/>
@@ -4427,8 +4654,9 @@
       <c r="L155" s="16"/>
       <c r="M155" s="16"/>
       <c r="N155" s="17"/>
-    </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O155" s="17"/>
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A156" s="13"/>
       <c r="B156" s="14"/>
       <c r="C156" s="14"/>
@@ -4449,8 +4677,9 @@
       <c r="L156" s="16"/>
       <c r="M156" s="16"/>
       <c r="N156" s="17"/>
-    </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O156" s="17"/>
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A157" s="13"/>
       <c r="B157" s="14"/>
       <c r="C157" s="14"/>
@@ -4471,8 +4700,9 @@
       <c r="L157" s="16"/>
       <c r="M157" s="16"/>
       <c r="N157" s="17"/>
-    </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O157" s="17"/>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A158" s="13"/>
       <c r="B158" s="14"/>
       <c r="C158" s="14"/>
@@ -4493,8 +4723,9 @@
       <c r="L158" s="16"/>
       <c r="M158" s="16"/>
       <c r="N158" s="17"/>
-    </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O158" s="17"/>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A159" s="13"/>
       <c r="B159" s="14"/>
       <c r="C159" s="14"/>
@@ -4515,8 +4746,9 @@
       <c r="L159" s="16"/>
       <c r="M159" s="16"/>
       <c r="N159" s="17"/>
-    </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O159" s="17"/>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A160" s="13"/>
       <c r="B160" s="14"/>
       <c r="C160" s="14"/>
@@ -4537,8 +4769,9 @@
       <c r="L160" s="16"/>
       <c r="M160" s="16"/>
       <c r="N160" s="17"/>
-    </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O160" s="17"/>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A161" s="13"/>
       <c r="B161" s="14"/>
       <c r="C161" s="14"/>
@@ -4559,8 +4792,9 @@
       <c r="L161" s="16"/>
       <c r="M161" s="16"/>
       <c r="N161" s="17"/>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O161" s="17"/>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A162" s="13"/>
       <c r="B162" s="14"/>
       <c r="C162" s="14"/>
@@ -4581,8 +4815,9 @@
       <c r="L162" s="16"/>
       <c r="M162" s="16"/>
       <c r="N162" s="17"/>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O162" s="17"/>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A163" s="13"/>
       <c r="B163" s="14"/>
       <c r="C163" s="14"/>
@@ -4603,8 +4838,9 @@
       <c r="L163" s="16"/>
       <c r="M163" s="16"/>
       <c r="N163" s="17"/>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O163" s="17"/>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A164" s="13"/>
       <c r="B164" s="14"/>
       <c r="C164" s="14"/>
@@ -4625,8 +4861,9 @@
       <c r="L164" s="16"/>
       <c r="M164" s="16"/>
       <c r="N164" s="17"/>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O164" s="17"/>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A165" s="13"/>
       <c r="B165" s="14"/>
       <c r="C165" s="14"/>
@@ -4647,8 +4884,9 @@
       <c r="L165" s="16"/>
       <c r="M165" s="16"/>
       <c r="N165" s="17"/>
-    </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O165" s="17"/>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A166" s="13"/>
       <c r="B166" s="14"/>
       <c r="C166" s="14"/>
@@ -4669,8 +4907,9 @@
       <c r="L166" s="16"/>
       <c r="M166" s="16"/>
       <c r="N166" s="17"/>
-    </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O166" s="17"/>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A167" s="13"/>
       <c r="B167" s="14"/>
       <c r="C167" s="14"/>
@@ -4691,8 +4930,9 @@
       <c r="L167" s="16"/>
       <c r="M167" s="16"/>
       <c r="N167" s="17"/>
-    </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O167" s="17"/>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A168" s="13"/>
       <c r="B168" s="14"/>
       <c r="C168" s="14"/>
@@ -4713,8 +4953,9 @@
       <c r="L168" s="16"/>
       <c r="M168" s="16"/>
       <c r="N168" s="17"/>
-    </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O168" s="17"/>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A169" s="13"/>
       <c r="B169" s="14"/>
       <c r="C169" s="14"/>
@@ -4735,8 +4976,9 @@
       <c r="L169" s="16"/>
       <c r="M169" s="16"/>
       <c r="N169" s="17"/>
-    </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O169" s="17"/>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A170" s="13"/>
       <c r="B170" s="14"/>
       <c r="C170" s="14"/>
@@ -4757,8 +4999,9 @@
       <c r="L170" s="16"/>
       <c r="M170" s="16"/>
       <c r="N170" s="17"/>
-    </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O170" s="17"/>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A171" s="13"/>
       <c r="B171" s="14"/>
       <c r="C171" s="14"/>
@@ -4779,8 +5022,9 @@
       <c r="L171" s="16"/>
       <c r="M171" s="16"/>
       <c r="N171" s="17"/>
-    </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O171" s="17"/>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A172" s="13"/>
       <c r="B172" s="14"/>
       <c r="C172" s="14"/>
@@ -4801,8 +5045,9 @@
       <c r="L172" s="16"/>
       <c r="M172" s="16"/>
       <c r="N172" s="17"/>
-    </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O172" s="17"/>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A173" s="13"/>
       <c r="B173" s="14"/>
       <c r="C173" s="14"/>
@@ -4823,8 +5068,9 @@
       <c r="L173" s="16"/>
       <c r="M173" s="16"/>
       <c r="N173" s="17"/>
-    </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O173" s="17"/>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A174" s="13"/>
       <c r="B174" s="14"/>
       <c r="C174" s="14"/>
@@ -4845,8 +5091,9 @@
       <c r="L174" s="16"/>
       <c r="M174" s="16"/>
       <c r="N174" s="17"/>
-    </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O174" s="17"/>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A175" s="13"/>
       <c r="B175" s="14"/>
       <c r="C175" s="14"/>
@@ -4867,8 +5114,9 @@
       <c r="L175" s="16"/>
       <c r="M175" s="16"/>
       <c r="N175" s="17"/>
-    </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O175" s="17"/>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A176" s="13"/>
       <c r="B176" s="14"/>
       <c r="C176" s="14"/>
@@ -4889,8 +5137,9 @@
       <c r="L176" s="16"/>
       <c r="M176" s="16"/>
       <c r="N176" s="17"/>
-    </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O176" s="17"/>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A177" s="13"/>
       <c r="B177" s="14"/>
       <c r="C177" s="14"/>
@@ -4911,8 +5160,9 @@
       <c r="L177" s="16"/>
       <c r="M177" s="16"/>
       <c r="N177" s="17"/>
-    </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O177" s="17"/>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A178" s="13"/>
       <c r="B178" s="14"/>
       <c r="C178" s="14"/>
@@ -4933,8 +5183,9 @@
       <c r="L178" s="16"/>
       <c r="M178" s="16"/>
       <c r="N178" s="17"/>
-    </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O178" s="17"/>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A179" s="13"/>
       <c r="B179" s="14"/>
       <c r="C179" s="14"/>
@@ -4955,8 +5206,9 @@
       <c r="L179" s="16"/>
       <c r="M179" s="16"/>
       <c r="N179" s="17"/>
-    </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O179" s="17"/>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A180" s="13"/>
       <c r="B180" s="14"/>
       <c r="C180" s="14"/>
@@ -4977,8 +5229,9 @@
       <c r="L180" s="16"/>
       <c r="M180" s="16"/>
       <c r="N180" s="17"/>
-    </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O180" s="17"/>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A181" s="13"/>
       <c r="B181" s="14"/>
       <c r="C181" s="14"/>
@@ -4999,8 +5252,9 @@
       <c r="L181" s="16"/>
       <c r="M181" s="16"/>
       <c r="N181" s="17"/>
-    </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O181" s="17"/>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A182" s="13"/>
       <c r="B182" s="14"/>
       <c r="C182" s="14"/>
@@ -5021,8 +5275,9 @@
       <c r="L182" s="16"/>
       <c r="M182" s="16"/>
       <c r="N182" s="17"/>
-    </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O182" s="17"/>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A183" s="13"/>
       <c r="B183" s="14"/>
       <c r="C183" s="14"/>
@@ -5043,8 +5298,9 @@
       <c r="L183" s="16"/>
       <c r="M183" s="16"/>
       <c r="N183" s="17"/>
-    </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O183" s="17"/>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A184" s="13"/>
       <c r="B184" s="14"/>
       <c r="C184" s="14"/>
@@ -5065,8 +5321,9 @@
       <c r="L184" s="16"/>
       <c r="M184" s="16"/>
       <c r="N184" s="17"/>
-    </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O184" s="17"/>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A185" s="13"/>
       <c r="B185" s="14"/>
       <c r="C185" s="14"/>
@@ -5087,8 +5344,9 @@
       <c r="L185" s="16"/>
       <c r="M185" s="16"/>
       <c r="N185" s="17"/>
-    </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O185" s="17"/>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A186" s="13"/>
       <c r="B186" s="14"/>
       <c r="C186" s="14"/>
@@ -5109,8 +5367,9 @@
       <c r="L186" s="16"/>
       <c r="M186" s="16"/>
       <c r="N186" s="17"/>
-    </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O186" s="17"/>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A187" s="13"/>
       <c r="B187" s="14"/>
       <c r="C187" s="14"/>
@@ -5131,8 +5390,9 @@
       <c r="L187" s="16"/>
       <c r="M187" s="16"/>
       <c r="N187" s="17"/>
-    </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O187" s="17"/>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A188" s="13"/>
       <c r="B188" s="14"/>
       <c r="C188" s="14"/>
@@ -5153,8 +5413,9 @@
       <c r="L188" s="16"/>
       <c r="M188" s="16"/>
       <c r="N188" s="17"/>
-    </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O188" s="17"/>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A189" s="13"/>
       <c r="B189" s="14"/>
       <c r="C189" s="14"/>
@@ -5175,8 +5436,9 @@
       <c r="L189" s="16"/>
       <c r="M189" s="16"/>
       <c r="N189" s="17"/>
-    </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O189" s="17"/>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A190" s="13"/>
       <c r="B190" s="14"/>
       <c r="C190" s="14"/>
@@ -5197,8 +5459,9 @@
       <c r="L190" s="16"/>
       <c r="M190" s="16"/>
       <c r="N190" s="17"/>
-    </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O190" s="17"/>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A191" s="13"/>
       <c r="B191" s="14"/>
       <c r="C191" s="14"/>
@@ -5219,8 +5482,9 @@
       <c r="L191" s="16"/>
       <c r="M191" s="16"/>
       <c r="N191" s="17"/>
-    </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O191" s="17"/>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A192" s="13"/>
       <c r="B192" s="14"/>
       <c r="C192" s="14"/>
@@ -5241,8 +5505,9 @@
       <c r="L192" s="16"/>
       <c r="M192" s="16"/>
       <c r="N192" s="17"/>
-    </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O192" s="17"/>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A193" s="13"/>
       <c r="B193" s="14"/>
       <c r="C193" s="14"/>
@@ -5263,8 +5528,9 @@
       <c r="L193" s="16"/>
       <c r="M193" s="16"/>
       <c r="N193" s="17"/>
-    </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O193" s="17"/>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A194" s="13"/>
       <c r="B194" s="14"/>
       <c r="C194" s="14"/>
@@ -5285,8 +5551,9 @@
       <c r="L194" s="16"/>
       <c r="M194" s="16"/>
       <c r="N194" s="17"/>
-    </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O194" s="17"/>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A195" s="13"/>
       <c r="B195" s="14"/>
       <c r="C195" s="14"/>
@@ -5307,8 +5574,9 @@
       <c r="L195" s="16"/>
       <c r="M195" s="16"/>
       <c r="N195" s="17"/>
-    </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O195" s="17"/>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A196" s="13"/>
       <c r="B196" s="14"/>
       <c r="C196" s="14"/>
@@ -5329,8 +5597,9 @@
       <c r="L196" s="16"/>
       <c r="M196" s="16"/>
       <c r="N196" s="17"/>
-    </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O196" s="17"/>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A197" s="13"/>
       <c r="B197" s="14"/>
       <c r="C197" s="14"/>
@@ -5351,8 +5620,9 @@
       <c r="L197" s="16"/>
       <c r="M197" s="16"/>
       <c r="N197" s="17"/>
-    </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O197" s="17"/>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A198" s="13"/>
       <c r="B198" s="14"/>
       <c r="C198" s="14"/>
@@ -5373,8 +5643,9 @@
       <c r="L198" s="16"/>
       <c r="M198" s="16"/>
       <c r="N198" s="17"/>
-    </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O198" s="17"/>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A199" s="13"/>
       <c r="B199" s="14"/>
       <c r="C199" s="14"/>
@@ -5395,8 +5666,9 @@
       <c r="L199" s="16"/>
       <c r="M199" s="16"/>
       <c r="N199" s="17"/>
-    </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O199" s="17"/>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A200" s="13"/>
       <c r="B200" s="14"/>
       <c r="C200" s="14"/>
@@ -5417,8 +5689,9 @@
       <c r="L200" s="16"/>
       <c r="M200" s="16"/>
       <c r="N200" s="17"/>
-    </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O200" s="17"/>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A201" s="13"/>
       <c r="B201" s="14"/>
       <c r="C201" s="14"/>
@@ -5439,8 +5712,9 @@
       <c r="L201" s="16"/>
       <c r="M201" s="16"/>
       <c r="N201" s="17"/>
-    </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O201" s="17"/>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A202" s="13"/>
       <c r="B202" s="14"/>
       <c r="C202" s="14"/>
@@ -5461,8 +5735,9 @@
       <c r="L202" s="16"/>
       <c r="M202" s="16"/>
       <c r="N202" s="17"/>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O202" s="17"/>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A203" s="13"/>
       <c r="B203" s="14"/>
       <c r="C203" s="14"/>
@@ -5483,8 +5758,9 @@
       <c r="L203" s="16"/>
       <c r="M203" s="16"/>
       <c r="N203" s="17"/>
-    </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O203" s="17"/>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A204" s="13"/>
       <c r="B204" s="14"/>
       <c r="C204" s="14"/>
@@ -5505,8 +5781,9 @@
       <c r="L204" s="16"/>
       <c r="M204" s="16"/>
       <c r="N204" s="17"/>
-    </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O204" s="17"/>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A205" s="13"/>
       <c r="B205" s="14"/>
       <c r="C205" s="14"/>
@@ -5527,8 +5804,9 @@
       <c r="L205" s="16"/>
       <c r="M205" s="16"/>
       <c r="N205" s="17"/>
-    </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O205" s="17"/>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A206" s="13"/>
       <c r="B206" s="14"/>
       <c r="C206" s="14"/>
@@ -5549,8 +5827,9 @@
       <c r="L206" s="16"/>
       <c r="M206" s="16"/>
       <c r="N206" s="17"/>
-    </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O206" s="17"/>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A207" s="13"/>
       <c r="B207" s="14"/>
       <c r="C207" s="14"/>
@@ -5571,8 +5850,9 @@
       <c r="L207" s="16"/>
       <c r="M207" s="16"/>
       <c r="N207" s="17"/>
-    </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O207" s="17"/>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A208" s="13"/>
       <c r="B208" s="14"/>
       <c r="C208" s="14"/>
@@ -5593,8 +5873,9 @@
       <c r="L208" s="16"/>
       <c r="M208" s="16"/>
       <c r="N208" s="17"/>
-    </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O208" s="17"/>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A209" s="13"/>
       <c r="B209" s="14"/>
       <c r="C209" s="14"/>
@@ -5615,8 +5896,9 @@
       <c r="L209" s="16"/>
       <c r="M209" s="16"/>
       <c r="N209" s="17"/>
-    </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O209" s="17"/>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A210" s="13"/>
       <c r="B210" s="14"/>
       <c r="C210" s="14"/>
@@ -5637,8 +5919,9 @@
       <c r="L210" s="16"/>
       <c r="M210" s="16"/>
       <c r="N210" s="17"/>
-    </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O210" s="17"/>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A211" s="13"/>
       <c r="B211" s="14"/>
       <c r="C211" s="14"/>
@@ -5659,8 +5942,9 @@
       <c r="L211" s="16"/>
       <c r="M211" s="16"/>
       <c r="N211" s="17"/>
-    </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O211" s="17"/>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A212" s="13"/>
       <c r="B212" s="14"/>
       <c r="C212" s="14"/>
@@ -5681,8 +5965,9 @@
       <c r="L212" s="16"/>
       <c r="M212" s="16"/>
       <c r="N212" s="17"/>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O212" s="17"/>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A213" s="13"/>
       <c r="B213" s="14"/>
       <c r="C213" s="14"/>
@@ -5703,8 +5988,9 @@
       <c r="L213" s="16"/>
       <c r="M213" s="16"/>
       <c r="N213" s="17"/>
-    </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O213" s="17"/>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A214" s="13"/>
       <c r="B214" s="14"/>
       <c r="C214" s="14"/>
@@ -5725,8 +6011,9 @@
       <c r="L214" s="16"/>
       <c r="M214" s="16"/>
       <c r="N214" s="17"/>
-    </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O214" s="17"/>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A215" s="13"/>
       <c r="B215" s="14"/>
       <c r="C215" s="14"/>
@@ -5747,8 +6034,9 @@
       <c r="L215" s="16"/>
       <c r="M215" s="16"/>
       <c r="N215" s="17"/>
-    </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O215" s="17"/>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A216" s="13"/>
       <c r="B216" s="14"/>
       <c r="C216" s="14"/>
@@ -5769,8 +6057,9 @@
       <c r="L216" s="16"/>
       <c r="M216" s="16"/>
       <c r="N216" s="17"/>
-    </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O216" s="17"/>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A217" s="13"/>
       <c r="B217" s="14"/>
       <c r="C217" s="14"/>
@@ -5791,8 +6080,9 @@
       <c r="L217" s="16"/>
       <c r="M217" s="16"/>
       <c r="N217" s="17"/>
-    </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O217" s="17"/>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A218" s="13"/>
       <c r="B218" s="14"/>
       <c r="C218" s="14"/>
@@ -5813,8 +6103,9 @@
       <c r="L218" s="16"/>
       <c r="M218" s="16"/>
       <c r="N218" s="17"/>
-    </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O218" s="17"/>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A219" s="13"/>
       <c r="B219" s="14"/>
       <c r="C219" s="14"/>
@@ -5835,8 +6126,9 @@
       <c r="L219" s="16"/>
       <c r="M219" s="16"/>
       <c r="N219" s="17"/>
-    </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O219" s="17"/>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A220" s="13"/>
       <c r="B220" s="14"/>
       <c r="C220" s="14"/>
@@ -5857,8 +6149,9 @@
       <c r="L220" s="16"/>
       <c r="M220" s="16"/>
       <c r="N220" s="17"/>
-    </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O220" s="17"/>
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A221" s="13"/>
       <c r="B221" s="14"/>
       <c r="C221" s="14"/>
@@ -5879,8 +6172,9 @@
       <c r="L221" s="16"/>
       <c r="M221" s="16"/>
       <c r="N221" s="17"/>
-    </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O221" s="17"/>
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A222" s="13"/>
       <c r="B222" s="14"/>
       <c r="C222" s="14"/>
@@ -5901,8 +6195,9 @@
       <c r="L222" s="16"/>
       <c r="M222" s="16"/>
       <c r="N222" s="17"/>
-    </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O222" s="17"/>
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A223" s="13"/>
       <c r="B223" s="14"/>
       <c r="C223" s="14"/>
@@ -5923,8 +6218,9 @@
       <c r="L223" s="16"/>
       <c r="M223" s="16"/>
       <c r="N223" s="17"/>
-    </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O223" s="17"/>
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A224" s="13"/>
       <c r="B224" s="14"/>
       <c r="C224" s="14"/>
@@ -5945,8 +6241,9 @@
       <c r="L224" s="16"/>
       <c r="M224" s="16"/>
       <c r="N224" s="17"/>
-    </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O224" s="17"/>
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A225" s="13"/>
       <c r="B225" s="14"/>
       <c r="C225" s="14"/>
@@ -5967,8 +6264,9 @@
       <c r="L225" s="16"/>
       <c r="M225" s="16"/>
       <c r="N225" s="17"/>
-    </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O225" s="17"/>
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A226" s="13"/>
       <c r="B226" s="14"/>
       <c r="C226" s="14"/>
@@ -5989,8 +6287,9 @@
       <c r="L226" s="16"/>
       <c r="M226" s="16"/>
       <c r="N226" s="17"/>
-    </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O226" s="17"/>
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A227" s="13"/>
       <c r="B227" s="14"/>
       <c r="C227" s="14"/>
@@ -6011,8 +6310,9 @@
       <c r="L227" s="16"/>
       <c r="M227" s="16"/>
       <c r="N227" s="17"/>
-    </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O227" s="17"/>
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A228" s="13"/>
       <c r="B228" s="14"/>
       <c r="C228" s="14"/>
@@ -6033,8 +6333,9 @@
       <c r="L228" s="16"/>
       <c r="M228" s="16"/>
       <c r="N228" s="17"/>
-    </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O228" s="17"/>
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A229" s="13"/>
       <c r="B229" s="14"/>
       <c r="C229" s="14"/>
@@ -6055,8 +6356,9 @@
       <c r="L229" s="16"/>
       <c r="M229" s="16"/>
       <c r="N229" s="17"/>
-    </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O229" s="17"/>
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A230" s="13"/>
       <c r="B230" s="14"/>
       <c r="C230" s="14"/>
@@ -6077,8 +6379,9 @@
       <c r="L230" s="16"/>
       <c r="M230" s="16"/>
       <c r="N230" s="17"/>
-    </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O230" s="17"/>
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A231" s="13"/>
       <c r="B231" s="14"/>
       <c r="C231" s="14"/>
@@ -6099,8 +6402,9 @@
       <c r="L231" s="16"/>
       <c r="M231" s="16"/>
       <c r="N231" s="17"/>
-    </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O231" s="17"/>
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A232" s="13"/>
       <c r="B232" s="14"/>
       <c r="C232" s="14"/>
@@ -6121,8 +6425,9 @@
       <c r="L232" s="16"/>
       <c r="M232" s="16"/>
       <c r="N232" s="17"/>
-    </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O232" s="17"/>
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A233" s="13"/>
       <c r="B233" s="14"/>
       <c r="C233" s="14"/>
@@ -6143,8 +6448,9 @@
       <c r="L233" s="16"/>
       <c r="M233" s="16"/>
       <c r="N233" s="17"/>
-    </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O233" s="17"/>
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A234" s="13"/>
       <c r="B234" s="14"/>
       <c r="C234" s="14"/>
@@ -6165,8 +6471,9 @@
       <c r="L234" s="16"/>
       <c r="M234" s="16"/>
       <c r="N234" s="17"/>
-    </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O234" s="17"/>
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A235" s="13"/>
       <c r="B235" s="14"/>
       <c r="C235" s="14"/>
@@ -6187,8 +6494,9 @@
       <c r="L235" s="16"/>
       <c r="M235" s="16"/>
       <c r="N235" s="17"/>
-    </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O235" s="17"/>
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A236" s="13"/>
       <c r="B236" s="14"/>
       <c r="C236" s="14"/>
@@ -6209,8 +6517,9 @@
       <c r="L236" s="16"/>
       <c r="M236" s="16"/>
       <c r="N236" s="17"/>
-    </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O236" s="17"/>
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A237" s="13"/>
       <c r="B237" s="14"/>
       <c r="C237" s="14"/>
@@ -6231,8 +6540,9 @@
       <c r="L237" s="16"/>
       <c r="M237" s="16"/>
       <c r="N237" s="17"/>
-    </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O237" s="17"/>
+    </row>
+    <row r="238" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A238" s="13"/>
       <c r="B238" s="14"/>
       <c r="C238" s="14"/>
@@ -6253,8 +6563,9 @@
       <c r="L238" s="16"/>
       <c r="M238" s="16"/>
       <c r="N238" s="17"/>
-    </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O238" s="17"/>
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A239" s="13"/>
       <c r="B239" s="14"/>
       <c r="C239" s="14"/>
@@ -6275,8 +6586,9 @@
       <c r="L239" s="16"/>
       <c r="M239" s="16"/>
       <c r="N239" s="17"/>
-    </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O239" s="17"/>
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A240" s="13"/>
       <c r="B240" s="14"/>
       <c r="C240" s="14"/>
@@ -6297,8 +6609,9 @@
       <c r="L240" s="16"/>
       <c r="M240" s="16"/>
       <c r="N240" s="17"/>
-    </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O240" s="17"/>
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A241" s="13"/>
       <c r="B241" s="14"/>
       <c r="C241" s="14"/>
@@ -6319,8 +6632,9 @@
       <c r="L241" s="16"/>
       <c r="M241" s="16"/>
       <c r="N241" s="17"/>
-    </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O241" s="17"/>
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A242" s="13"/>
       <c r="B242" s="14"/>
       <c r="C242" s="14"/>
@@ -6341,8 +6655,9 @@
       <c r="L242" s="16"/>
       <c r="M242" s="16"/>
       <c r="N242" s="17"/>
-    </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O242" s="17"/>
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A243" s="13"/>
       <c r="B243" s="14"/>
       <c r="C243" s="14"/>
@@ -6363,8 +6678,9 @@
       <c r="L243" s="16"/>
       <c r="M243" s="16"/>
       <c r="N243" s="17"/>
-    </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O243" s="17"/>
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A244" s="13"/>
       <c r="B244" s="14"/>
       <c r="C244" s="14"/>
@@ -6385,8 +6701,9 @@
       <c r="L244" s="16"/>
       <c r="M244" s="16"/>
       <c r="N244" s="17"/>
-    </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O244" s="17"/>
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A245" s="13"/>
       <c r="B245" s="14"/>
       <c r="C245" s="14"/>
@@ -6407,8 +6724,9 @@
       <c r="L245" s="16"/>
       <c r="M245" s="16"/>
       <c r="N245" s="17"/>
-    </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O245" s="17"/>
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A246" s="13"/>
       <c r="B246" s="14"/>
       <c r="C246" s="14"/>
@@ -6429,8 +6747,9 @@
       <c r="L246" s="16"/>
       <c r="M246" s="16"/>
       <c r="N246" s="17"/>
-    </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O246" s="17"/>
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A247" s="13"/>
       <c r="B247" s="14"/>
       <c r="C247" s="14"/>
@@ -6451,8 +6770,9 @@
       <c r="L247" s="16"/>
       <c r="M247" s="16"/>
       <c r="N247" s="17"/>
-    </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O247" s="17"/>
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A248" s="13"/>
       <c r="B248" s="14"/>
       <c r="C248" s="14"/>
@@ -6473,8 +6793,9 @@
       <c r="L248" s="16"/>
       <c r="M248" s="16"/>
       <c r="N248" s="17"/>
-    </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O248" s="17"/>
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A249" s="13"/>
       <c r="B249" s="14"/>
       <c r="C249" s="14"/>
@@ -6495,8 +6816,9 @@
       <c r="L249" s="16"/>
       <c r="M249" s="16"/>
       <c r="N249" s="17"/>
-    </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O249" s="17"/>
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A250" s="13"/>
       <c r="B250" s="14"/>
       <c r="C250" s="14"/>
@@ -6517,8 +6839,9 @@
       <c r="L250" s="16"/>
       <c r="M250" s="16"/>
       <c r="N250" s="17"/>
-    </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O250" s="17"/>
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A251" s="13"/>
       <c r="B251" s="14"/>
       <c r="C251" s="14"/>
@@ -6539,8 +6862,9 @@
       <c r="L251" s="16"/>
       <c r="M251" s="16"/>
       <c r="N251" s="17"/>
-    </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O251" s="17"/>
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A252" s="13"/>
       <c r="B252" s="14"/>
       <c r="C252" s="14"/>
@@ -6561,8 +6885,9 @@
       <c r="L252" s="16"/>
       <c r="M252" s="16"/>
       <c r="N252" s="17"/>
-    </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O252" s="17"/>
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A253" s="13"/>
       <c r="B253" s="14"/>
       <c r="C253" s="14"/>
@@ -6583,8 +6908,9 @@
       <c r="L253" s="16"/>
       <c r="M253" s="16"/>
       <c r="N253" s="17"/>
-    </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O253" s="17"/>
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A254" s="13"/>
       <c r="B254" s="14"/>
       <c r="C254" s="14"/>
@@ -6605,8 +6931,9 @@
       <c r="L254" s="16"/>
       <c r="M254" s="16"/>
       <c r="N254" s="17"/>
-    </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O254" s="17"/>
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A255" s="13"/>
       <c r="B255" s="14"/>
       <c r="C255" s="14"/>
@@ -6627,8 +6954,9 @@
       <c r="L255" s="16"/>
       <c r="M255" s="16"/>
       <c r="N255" s="17"/>
-    </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O255" s="17"/>
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A256" s="13"/>
       <c r="B256" s="14"/>
       <c r="C256" s="14"/>
@@ -6649,8 +6977,9 @@
       <c r="L256" s="16"/>
       <c r="M256" s="16"/>
       <c r="N256" s="17"/>
-    </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O256" s="17"/>
+    </row>
+    <row r="257" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A257" s="13"/>
       <c r="B257" s="14"/>
       <c r="C257" s="14"/>
@@ -6671,8 +7000,9 @@
       <c r="L257" s="16"/>
       <c r="M257" s="16"/>
       <c r="N257" s="17"/>
-    </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O257" s="17"/>
+    </row>
+    <row r="258" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A258" s="13"/>
       <c r="B258" s="14"/>
       <c r="C258" s="14"/>
@@ -6693,8 +7023,9 @@
       <c r="L258" s="16"/>
       <c r="M258" s="16"/>
       <c r="N258" s="17"/>
-    </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O258" s="17"/>
+    </row>
+    <row r="259" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A259" s="13"/>
       <c r="B259" s="14"/>
       <c r="C259" s="14"/>
@@ -6715,8 +7046,9 @@
       <c r="L259" s="16"/>
       <c r="M259" s="16"/>
       <c r="N259" s="17"/>
-    </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O259" s="17"/>
+    </row>
+    <row r="260" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A260" s="13"/>
       <c r="B260" s="14"/>
       <c r="C260" s="14"/>
@@ -6737,8 +7069,9 @@
       <c r="L260" s="16"/>
       <c r="M260" s="16"/>
       <c r="N260" s="17"/>
-    </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O260" s="17"/>
+    </row>
+    <row r="261" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A261" s="13"/>
       <c r="B261" s="14"/>
       <c r="C261" s="14"/>
@@ -6759,8 +7092,9 @@
       <c r="L261" s="16"/>
       <c r="M261" s="16"/>
       <c r="N261" s="17"/>
-    </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O261" s="17"/>
+    </row>
+    <row r="262" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A262" s="13"/>
       <c r="B262" s="14"/>
       <c r="C262" s="14"/>
@@ -6781,8 +7115,9 @@
       <c r="L262" s="16"/>
       <c r="M262" s="16"/>
       <c r="N262" s="17"/>
-    </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O262" s="17"/>
+    </row>
+    <row r="263" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A263" s="13"/>
       <c r="B263" s="14"/>
       <c r="C263" s="14"/>
@@ -6803,8 +7138,9 @@
       <c r="L263" s="16"/>
       <c r="M263" s="16"/>
       <c r="N263" s="17"/>
-    </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O263" s="17"/>
+    </row>
+    <row r="264" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A264" s="13"/>
       <c r="B264" s="14"/>
       <c r="C264" s="14"/>
@@ -6825,8 +7161,9 @@
       <c r="L264" s="16"/>
       <c r="M264" s="16"/>
       <c r="N264" s="17"/>
-    </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O264" s="17"/>
+    </row>
+    <row r="265" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A265" s="13"/>
       <c r="B265" s="14"/>
       <c r="C265" s="14"/>
@@ -6847,8 +7184,9 @@
       <c r="L265" s="16"/>
       <c r="M265" s="16"/>
       <c r="N265" s="17"/>
-    </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O265" s="17"/>
+    </row>
+    <row r="266" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A266" s="13"/>
       <c r="B266" s="14"/>
       <c r="C266" s="14"/>
@@ -6869,8 +7207,9 @@
       <c r="L266" s="16"/>
       <c r="M266" s="16"/>
       <c r="N266" s="17"/>
-    </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O266" s="17"/>
+    </row>
+    <row r="267" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A267" s="13"/>
       <c r="B267" s="14"/>
       <c r="C267" s="14"/>
@@ -6891,8 +7230,9 @@
       <c r="L267" s="16"/>
       <c r="M267" s="16"/>
       <c r="N267" s="17"/>
-    </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O267" s="17"/>
+    </row>
+    <row r="268" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A268" s="13"/>
       <c r="B268" s="14"/>
       <c r="C268" s="14"/>
@@ -6913,8 +7253,9 @@
       <c r="L268" s="16"/>
       <c r="M268" s="16"/>
       <c r="N268" s="17"/>
-    </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O268" s="17"/>
+    </row>
+    <row r="269" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A269" s="13"/>
       <c r="B269" s="14"/>
       <c r="C269" s="14"/>
@@ -6935,8 +7276,9 @@
       <c r="L269" s="16"/>
       <c r="M269" s="16"/>
       <c r="N269" s="17"/>
-    </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O269" s="17"/>
+    </row>
+    <row r="270" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A270" s="13"/>
       <c r="B270" s="14"/>
       <c r="C270" s="14"/>
@@ -6957,8 +7299,9 @@
       <c r="L270" s="16"/>
       <c r="M270" s="16"/>
       <c r="N270" s="17"/>
-    </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O270" s="17"/>
+    </row>
+    <row r="271" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A271" s="13"/>
       <c r="B271" s="14"/>
       <c r="C271" s="14"/>
@@ -6979,8 +7322,9 @@
       <c r="L271" s="16"/>
       <c r="M271" s="16"/>
       <c r="N271" s="17"/>
-    </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O271" s="17"/>
+    </row>
+    <row r="272" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A272" s="13"/>
       <c r="B272" s="14"/>
       <c r="C272" s="14"/>
@@ -7001,8 +7345,9 @@
       <c r="L272" s="16"/>
       <c r="M272" s="16"/>
       <c r="N272" s="17"/>
-    </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O272" s="17"/>
+    </row>
+    <row r="273" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A273" s="13"/>
       <c r="B273" s="14"/>
       <c r="C273" s="14"/>
@@ -7023,8 +7368,9 @@
       <c r="L273" s="16"/>
       <c r="M273" s="16"/>
       <c r="N273" s="17"/>
-    </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O273" s="17"/>
+    </row>
+    <row r="274" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A274" s="13"/>
       <c r="B274" s="14"/>
       <c r="C274" s="14"/>
@@ -7045,8 +7391,9 @@
       <c r="L274" s="16"/>
       <c r="M274" s="16"/>
       <c r="N274" s="17"/>
-    </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O274" s="17"/>
+    </row>
+    <row r="275" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A275" s="13"/>
       <c r="B275" s="14"/>
       <c r="C275" s="14"/>
@@ -7067,8 +7414,9 @@
       <c r="L275" s="16"/>
       <c r="M275" s="16"/>
       <c r="N275" s="17"/>
-    </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O275" s="17"/>
+    </row>
+    <row r="276" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A276" s="13"/>
       <c r="B276" s="14"/>
       <c r="C276" s="14"/>
@@ -7089,8 +7437,9 @@
       <c r="L276" s="16"/>
       <c r="M276" s="16"/>
       <c r="N276" s="17"/>
-    </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O276" s="17"/>
+    </row>
+    <row r="277" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A277" s="13"/>
       <c r="B277" s="14"/>
       <c r="C277" s="14"/>
@@ -7111,8 +7460,9 @@
       <c r="L277" s="16"/>
       <c r="M277" s="16"/>
       <c r="N277" s="17"/>
-    </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O277" s="17"/>
+    </row>
+    <row r="278" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A278" s="13"/>
       <c r="B278" s="14"/>
       <c r="C278" s="14"/>
@@ -7133,8 +7483,9 @@
       <c r="L278" s="16"/>
       <c r="M278" s="16"/>
       <c r="N278" s="17"/>
-    </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O278" s="17"/>
+    </row>
+    <row r="279" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A279" s="13"/>
       <c r="B279" s="14"/>
       <c r="C279" s="14"/>
@@ -7155,8 +7506,9 @@
       <c r="L279" s="16"/>
       <c r="M279" s="16"/>
       <c r="N279" s="17"/>
-    </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O279" s="17"/>
+    </row>
+    <row r="280" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A280" s="13"/>
       <c r="B280" s="14"/>
       <c r="C280" s="14"/>
@@ -7177,8 +7529,9 @@
       <c r="L280" s="16"/>
       <c r="M280" s="16"/>
       <c r="N280" s="17"/>
-    </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O280" s="17"/>
+    </row>
+    <row r="281" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A281" s="13"/>
       <c r="B281" s="14"/>
       <c r="C281" s="14"/>
@@ -7199,8 +7552,9 @@
       <c r="L281" s="16"/>
       <c r="M281" s="16"/>
       <c r="N281" s="17"/>
-    </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O281" s="17"/>
+    </row>
+    <row r="282" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A282" s="13"/>
       <c r="B282" s="14"/>
       <c r="C282" s="14"/>
@@ -7221,8 +7575,9 @@
       <c r="L282" s="16"/>
       <c r="M282" s="16"/>
       <c r="N282" s="17"/>
-    </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O282" s="17"/>
+    </row>
+    <row r="283" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A283" s="13"/>
       <c r="B283" s="14"/>
       <c r="C283" s="14"/>
@@ -7243,8 +7598,9 @@
       <c r="L283" s="16"/>
       <c r="M283" s="16"/>
       <c r="N283" s="17"/>
-    </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O283" s="17"/>
+    </row>
+    <row r="284" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A284" s="13"/>
       <c r="B284" s="14"/>
       <c r="C284" s="14"/>
@@ -7265,8 +7621,9 @@
       <c r="L284" s="16"/>
       <c r="M284" s="16"/>
       <c r="N284" s="17"/>
-    </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O284" s="17"/>
+    </row>
+    <row r="285" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A285" s="13"/>
       <c r="B285" s="14"/>
       <c r="C285" s="14"/>
@@ -7287,8 +7644,9 @@
       <c r="L285" s="16"/>
       <c r="M285" s="16"/>
       <c r="N285" s="17"/>
-    </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O285" s="17"/>
+    </row>
+    <row r="286" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A286" s="13"/>
       <c r="B286" s="14"/>
       <c r="C286" s="14"/>
@@ -7309,8 +7667,9 @@
       <c r="L286" s="16"/>
       <c r="M286" s="16"/>
       <c r="N286" s="17"/>
-    </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O286" s="17"/>
+    </row>
+    <row r="287" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A287" s="13"/>
       <c r="B287" s="14"/>
       <c r="C287" s="14"/>
@@ -7331,8 +7690,9 @@
       <c r="L287" s="16"/>
       <c r="M287" s="16"/>
       <c r="N287" s="17"/>
-    </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O287" s="17"/>
+    </row>
+    <row r="288" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A288" s="13"/>
       <c r="B288" s="14"/>
       <c r="C288" s="14"/>
@@ -7353,8 +7713,9 @@
       <c r="L288" s="16"/>
       <c r="M288" s="16"/>
       <c r="N288" s="17"/>
-    </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O288" s="17"/>
+    </row>
+    <row r="289" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A289" s="13"/>
       <c r="B289" s="14"/>
       <c r="C289" s="14"/>
@@ -7375,8 +7736,9 @@
       <c r="L289" s="16"/>
       <c r="M289" s="16"/>
       <c r="N289" s="17"/>
-    </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O289" s="17"/>
+    </row>
+    <row r="290" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A290" s="13"/>
       <c r="B290" s="14"/>
       <c r="C290" s="14"/>
@@ -7397,8 +7759,9 @@
       <c r="L290" s="16"/>
       <c r="M290" s="16"/>
       <c r="N290" s="17"/>
-    </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O290" s="17"/>
+    </row>
+    <row r="291" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A291" s="13"/>
       <c r="B291" s="14"/>
       <c r="C291" s="14"/>
@@ -7419,8 +7782,9 @@
       <c r="L291" s="16"/>
       <c r="M291" s="16"/>
       <c r="N291" s="17"/>
-    </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O291" s="17"/>
+    </row>
+    <row r="292" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A292" s="13"/>
       <c r="B292" s="14"/>
       <c r="C292" s="14"/>
@@ -7441,8 +7805,9 @@
       <c r="L292" s="16"/>
       <c r="M292" s="16"/>
       <c r="N292" s="17"/>
-    </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O292" s="17"/>
+    </row>
+    <row r="293" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A293" s="13"/>
       <c r="B293" s="14"/>
       <c r="C293" s="14"/>
@@ -7463,8 +7828,9 @@
       <c r="L293" s="16"/>
       <c r="M293" s="16"/>
       <c r="N293" s="17"/>
-    </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O293" s="17"/>
+    </row>
+    <row r="294" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A294" s="13"/>
       <c r="B294" s="14"/>
       <c r="C294" s="14"/>
@@ -7485,8 +7851,9 @@
       <c r="L294" s="16"/>
       <c r="M294" s="16"/>
       <c r="N294" s="17"/>
-    </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O294" s="17"/>
+    </row>
+    <row r="295" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A295" s="13"/>
       <c r="B295" s="14"/>
       <c r="C295" s="14"/>
@@ -7507,8 +7874,9 @@
       <c r="L295" s="16"/>
       <c r="M295" s="16"/>
       <c r="N295" s="17"/>
-    </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O295" s="17"/>
+    </row>
+    <row r="296" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A296" s="13"/>
       <c r="B296" s="14"/>
       <c r="C296" s="14"/>
@@ -7529,8 +7897,9 @@
       <c r="L296" s="16"/>
       <c r="M296" s="16"/>
       <c r="N296" s="17"/>
-    </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O296" s="17"/>
+    </row>
+    <row r="297" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A297" s="13"/>
       <c r="B297" s="14"/>
       <c r="C297" s="14"/>
@@ -7551,8 +7920,9 @@
       <c r="L297" s="16"/>
       <c r="M297" s="16"/>
       <c r="N297" s="17"/>
-    </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O297" s="17"/>
+    </row>
+    <row r="298" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A298" s="13"/>
       <c r="B298" s="14"/>
       <c r="C298" s="14"/>
@@ -7573,8 +7943,9 @@
       <c r="L298" s="16"/>
       <c r="M298" s="16"/>
       <c r="N298" s="17"/>
-    </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O298" s="17"/>
+    </row>
+    <row r="299" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A299" s="13"/>
       <c r="B299" s="14"/>
       <c r="C299" s="14"/>
@@ -7595,8 +7966,9 @@
       <c r="L299" s="16"/>
       <c r="M299" s="16"/>
       <c r="N299" s="17"/>
-    </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O299" s="17"/>
+    </row>
+    <row r="300" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A300" s="13"/>
       <c r="B300" s="14"/>
       <c r="C300" s="14"/>
@@ -7617,8 +7989,9 @@
       <c r="L300" s="16"/>
       <c r="M300" s="16"/>
       <c r="N300" s="17"/>
-    </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O300" s="17"/>
+    </row>
+    <row r="301" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A301" s="13"/>
       <c r="B301" s="14"/>
       <c r="C301" s="14"/>
@@ -7639,8 +8012,9 @@
       <c r="L301" s="16"/>
       <c r="M301" s="16"/>
       <c r="N301" s="17"/>
-    </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O301" s="17"/>
+    </row>
+    <row r="302" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A302" s="13"/>
       <c r="B302" s="14"/>
       <c r="C302" s="14"/>
@@ -7661,8 +8035,9 @@
       <c r="L302" s="16"/>
       <c r="M302" s="16"/>
       <c r="N302" s="17"/>
-    </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O302" s="17"/>
+    </row>
+    <row r="303" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A303" s="13"/>
       <c r="B303" s="14"/>
       <c r="C303" s="14"/>
@@ -7683,8 +8058,9 @@
       <c r="L303" s="16"/>
       <c r="M303" s="16"/>
       <c r="N303" s="17"/>
-    </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O303" s="17"/>
+    </row>
+    <row r="304" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A304" s="13"/>
       <c r="B304" s="14"/>
       <c r="C304" s="14"/>
@@ -7705,8 +8081,9 @@
       <c r="L304" s="16"/>
       <c r="M304" s="16"/>
       <c r="N304" s="17"/>
-    </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O304" s="17"/>
+    </row>
+    <row r="305" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A305" s="13"/>
       <c r="B305" s="14"/>
       <c r="C305" s="14"/>
@@ -7727,8 +8104,9 @@
       <c r="L305" s="16"/>
       <c r="M305" s="16"/>
       <c r="N305" s="17"/>
-    </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O305" s="17"/>
+    </row>
+    <row r="306" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A306" s="13"/>
       <c r="B306" s="14"/>
       <c r="C306" s="14"/>
@@ -7749,8 +8127,9 @@
       <c r="L306" s="16"/>
       <c r="M306" s="16"/>
       <c r="N306" s="17"/>
-    </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O306" s="17"/>
+    </row>
+    <row r="307" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A307" s="13"/>
       <c r="B307" s="14"/>
       <c r="C307" s="14"/>
@@ -7771,8 +8150,9 @@
       <c r="L307" s="16"/>
       <c r="M307" s="16"/>
       <c r="N307" s="17"/>
-    </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O307" s="17"/>
+    </row>
+    <row r="308" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A308" s="13"/>
       <c r="B308" s="14"/>
       <c r="C308" s="14"/>
@@ -7793,8 +8173,9 @@
       <c r="L308" s="16"/>
       <c r="M308" s="16"/>
       <c r="N308" s="17"/>
-    </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O308" s="17"/>
+    </row>
+    <row r="309" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A309" s="13"/>
       <c r="B309" s="14"/>
       <c r="C309" s="14"/>
@@ -7815,8 +8196,9 @@
       <c r="L309" s="16"/>
       <c r="M309" s="16"/>
       <c r="N309" s="17"/>
-    </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O309" s="17"/>
+    </row>
+    <row r="310" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A310" s="13"/>
       <c r="B310" s="14"/>
       <c r="C310" s="14"/>
@@ -7837,8 +8219,9 @@
       <c r="L310" s="16"/>
       <c r="M310" s="16"/>
       <c r="N310" s="17"/>
-    </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O310" s="17"/>
+    </row>
+    <row r="311" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A311" s="13"/>
       <c r="B311" s="14"/>
       <c r="C311" s="14"/>
@@ -7859,8 +8242,9 @@
       <c r="L311" s="16"/>
       <c r="M311" s="16"/>
       <c r="N311" s="17"/>
-    </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O311" s="17"/>
+    </row>
+    <row r="312" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A312" s="13"/>
       <c r="B312" s="14"/>
       <c r="C312" s="14"/>
@@ -7881,8 +8265,9 @@
       <c r="L312" s="16"/>
       <c r="M312" s="16"/>
       <c r="N312" s="17"/>
-    </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O312" s="17"/>
+    </row>
+    <row r="313" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A313" s="13"/>
       <c r="B313" s="14"/>
       <c r="C313" s="14"/>
@@ -7903,8 +8288,9 @@
       <c r="L313" s="16"/>
       <c r="M313" s="16"/>
       <c r="N313" s="17"/>
-    </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O313" s="17"/>
+    </row>
+    <row r="314" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A314" s="13"/>
       <c r="B314" s="14"/>
       <c r="C314" s="14"/>
@@ -7925,8 +8311,9 @@
       <c r="L314" s="16"/>
       <c r="M314" s="16"/>
       <c r="N314" s="17"/>
-    </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O314" s="17"/>
+    </row>
+    <row r="315" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A315" s="13"/>
       <c r="B315" s="14"/>
       <c r="C315" s="14"/>
@@ -7947,8 +8334,9 @@
       <c r="L315" s="16"/>
       <c r="M315" s="16"/>
       <c r="N315" s="17"/>
-    </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O315" s="17"/>
+    </row>
+    <row r="316" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A316" s="13"/>
       <c r="B316" s="14"/>
       <c r="C316" s="14"/>
@@ -7969,8 +8357,9 @@
       <c r="L316" s="16"/>
       <c r="M316" s="16"/>
       <c r="N316" s="17"/>
-    </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O316" s="17"/>
+    </row>
+    <row r="317" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A317" s="13"/>
       <c r="B317" s="14"/>
       <c r="C317" s="14"/>
@@ -7991,8 +8380,9 @@
       <c r="L317" s="16"/>
       <c r="M317" s="16"/>
       <c r="N317" s="17"/>
-    </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O317" s="17"/>
+    </row>
+    <row r="318" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A318" s="13"/>
       <c r="B318" s="14"/>
       <c r="C318" s="14"/>
@@ -8013,8 +8403,9 @@
       <c r="L318" s="16"/>
       <c r="M318" s="16"/>
       <c r="N318" s="17"/>
-    </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O318" s="17"/>
+    </row>
+    <row r="319" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A319" s="13"/>
       <c r="B319" s="14"/>
       <c r="C319" s="14"/>
@@ -8035,8 +8426,9 @@
       <c r="L319" s="16"/>
       <c r="M319" s="16"/>
       <c r="N319" s="17"/>
-    </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O319" s="17"/>
+    </row>
+    <row r="320" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A320" s="13"/>
       <c r="B320" s="14"/>
       <c r="C320" s="14"/>
@@ -8057,8 +8449,9 @@
       <c r="L320" s="16"/>
       <c r="M320" s="16"/>
       <c r="N320" s="17"/>
-    </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O320" s="17"/>
+    </row>
+    <row r="321" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A321" s="13"/>
       <c r="B321" s="14"/>
       <c r="C321" s="14"/>
@@ -8079,8 +8472,9 @@
       <c r="L321" s="16"/>
       <c r="M321" s="16"/>
       <c r="N321" s="17"/>
-    </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O321" s="17"/>
+    </row>
+    <row r="322" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A322" s="13"/>
       <c r="B322" s="14"/>
       <c r="C322" s="14"/>
@@ -8101,8 +8495,9 @@
       <c r="L322" s="16"/>
       <c r="M322" s="16"/>
       <c r="N322" s="17"/>
-    </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O322" s="17"/>
+    </row>
+    <row r="323" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A323" s="13"/>
       <c r="B323" s="14"/>
       <c r="C323" s="14"/>
@@ -8123,8 +8518,9 @@
       <c r="L323" s="16"/>
       <c r="M323" s="16"/>
       <c r="N323" s="17"/>
-    </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O323" s="17"/>
+    </row>
+    <row r="324" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A324" s="13"/>
       <c r="B324" s="14"/>
       <c r="C324" s="14"/>
@@ -8145,8 +8541,9 @@
       <c r="L324" s="16"/>
       <c r="M324" s="16"/>
       <c r="N324" s="17"/>
-    </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O324" s="17"/>
+    </row>
+    <row r="325" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A325" s="13"/>
       <c r="B325" s="14"/>
       <c r="C325" s="14"/>
@@ -8167,8 +8564,9 @@
       <c r="L325" s="16"/>
       <c r="M325" s="16"/>
       <c r="N325" s="17"/>
-    </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O325" s="17"/>
+    </row>
+    <row r="326" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A326" s="13"/>
       <c r="B326" s="14"/>
       <c r="C326" s="14"/>
@@ -8189,8 +8587,9 @@
       <c r="L326" s="16"/>
       <c r="M326" s="16"/>
       <c r="N326" s="17"/>
-    </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O326" s="17"/>
+    </row>
+    <row r="327" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A327" s="13"/>
       <c r="B327" s="14"/>
       <c r="C327" s="14"/>
@@ -8211,8 +8610,9 @@
       <c r="L327" s="16"/>
       <c r="M327" s="16"/>
       <c r="N327" s="17"/>
-    </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O327" s="17"/>
+    </row>
+    <row r="328" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A328" s="13"/>
       <c r="B328" s="14"/>
       <c r="C328" s="14"/>
@@ -8233,8 +8633,9 @@
       <c r="L328" s="16"/>
       <c r="M328" s="16"/>
       <c r="N328" s="17"/>
-    </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O328" s="17"/>
+    </row>
+    <row r="329" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A329" s="13"/>
       <c r="B329" s="14"/>
       <c r="C329" s="14"/>
@@ -8255,8 +8656,9 @@
       <c r="L329" s="16"/>
       <c r="M329" s="16"/>
       <c r="N329" s="17"/>
-    </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O329" s="17"/>
+    </row>
+    <row r="330" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A330" s="13"/>
       <c r="B330" s="14"/>
       <c r="C330" s="14"/>
@@ -8277,8 +8679,9 @@
       <c r="L330" s="16"/>
       <c r="M330" s="16"/>
       <c r="N330" s="17"/>
-    </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O330" s="17"/>
+    </row>
+    <row r="331" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A331" s="13"/>
       <c r="B331" s="14"/>
       <c r="C331" s="14"/>
@@ -8299,8 +8702,9 @@
       <c r="L331" s="16"/>
       <c r="M331" s="16"/>
       <c r="N331" s="17"/>
-    </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O331" s="17"/>
+    </row>
+    <row r="332" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A332" s="13"/>
       <c r="B332" s="14"/>
       <c r="C332" s="14"/>
@@ -8321,8 +8725,9 @@
       <c r="L332" s="16"/>
       <c r="M332" s="16"/>
       <c r="N332" s="17"/>
-    </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O332" s="17"/>
+    </row>
+    <row r="333" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A333" s="13"/>
       <c r="B333" s="14"/>
       <c r="C333" s="14"/>
@@ -8343,8 +8748,9 @@
       <c r="L333" s="16"/>
       <c r="M333" s="16"/>
       <c r="N333" s="17"/>
-    </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O333" s="17"/>
+    </row>
+    <row r="334" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A334" s="13"/>
       <c r="B334" s="14"/>
       <c r="C334" s="14"/>
@@ -8365,8 +8771,9 @@
       <c r="L334" s="16"/>
       <c r="M334" s="16"/>
       <c r="N334" s="17"/>
-    </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O334" s="17"/>
+    </row>
+    <row r="335" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A335" s="13"/>
       <c r="B335" s="14"/>
       <c r="C335" s="14"/>
@@ -8387,8 +8794,9 @@
       <c r="L335" s="16"/>
       <c r="M335" s="16"/>
       <c r="N335" s="17"/>
-    </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O335" s="17"/>
+    </row>
+    <row r="336" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A336" s="13"/>
       <c r="B336" s="14"/>
       <c r="C336" s="14"/>
@@ -8409,8 +8817,9 @@
       <c r="L336" s="16"/>
       <c r="M336" s="16"/>
       <c r="N336" s="17"/>
-    </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O336" s="17"/>
+    </row>
+    <row r="337" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A337" s="13"/>
       <c r="B337" s="14"/>
       <c r="C337" s="14"/>
@@ -8431,8 +8840,9 @@
       <c r="L337" s="16"/>
       <c r="M337" s="16"/>
       <c r="N337" s="17"/>
-    </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O337" s="17"/>
+    </row>
+    <row r="338" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A338" s="13"/>
       <c r="B338" s="14"/>
       <c r="C338" s="14"/>
@@ -8453,8 +8863,9 @@
       <c r="L338" s="16"/>
       <c r="M338" s="16"/>
       <c r="N338" s="17"/>
-    </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O338" s="17"/>
+    </row>
+    <row r="339" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A339" s="13"/>
       <c r="B339" s="14"/>
       <c r="C339" s="14"/>
@@ -8475,8 +8886,9 @@
       <c r="L339" s="16"/>
       <c r="M339" s="16"/>
       <c r="N339" s="17"/>
-    </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O339" s="17"/>
+    </row>
+    <row r="340" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A340" s="13"/>
       <c r="B340" s="14"/>
       <c r="C340" s="14"/>
@@ -8497,8 +8909,9 @@
       <c r="L340" s="16"/>
       <c r="M340" s="16"/>
       <c r="N340" s="17"/>
-    </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O340" s="17"/>
+    </row>
+    <row r="341" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A341" s="13"/>
       <c r="B341" s="14"/>
       <c r="C341" s="14"/>
@@ -8519,8 +8932,9 @@
       <c r="L341" s="16"/>
       <c r="M341" s="16"/>
       <c r="N341" s="17"/>
-    </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O341" s="17"/>
+    </row>
+    <row r="342" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A342" s="13"/>
       <c r="B342" s="14"/>
       <c r="C342" s="14"/>
@@ -8541,8 +8955,9 @@
       <c r="L342" s="16"/>
       <c r="M342" s="16"/>
       <c r="N342" s="17"/>
-    </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O342" s="17"/>
+    </row>
+    <row r="343" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A343" s="13"/>
       <c r="B343" s="14"/>
       <c r="C343" s="14"/>
@@ -8563,8 +8978,9 @@
       <c r="L343" s="16"/>
       <c r="M343" s="16"/>
       <c r="N343" s="17"/>
-    </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O343" s="17"/>
+    </row>
+    <row r="344" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A344" s="13"/>
       <c r="B344" s="14"/>
       <c r="C344" s="14"/>
@@ -8585,8 +9001,9 @@
       <c r="L344" s="16"/>
       <c r="M344" s="16"/>
       <c r="N344" s="17"/>
-    </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O344" s="17"/>
+    </row>
+    <row r="345" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A345" s="13"/>
       <c r="B345" s="14"/>
       <c r="C345" s="14"/>
@@ -8607,8 +9024,9 @@
       <c r="L345" s="16"/>
       <c r="M345" s="16"/>
       <c r="N345" s="17"/>
-    </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O345" s="17"/>
+    </row>
+    <row r="346" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A346" s="13"/>
       <c r="B346" s="14"/>
       <c r="C346" s="14"/>
@@ -8629,8 +9047,9 @@
       <c r="L346" s="16"/>
       <c r="M346" s="16"/>
       <c r="N346" s="17"/>
-    </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O346" s="17"/>
+    </row>
+    <row r="347" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A347" s="13"/>
       <c r="B347" s="14"/>
       <c r="C347" s="14"/>
@@ -8651,8 +9070,9 @@
       <c r="L347" s="16"/>
       <c r="M347" s="16"/>
       <c r="N347" s="17"/>
-    </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O347" s="17"/>
+    </row>
+    <row r="348" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A348" s="13"/>
       <c r="B348" s="14"/>
       <c r="C348" s="14"/>
@@ -8673,8 +9093,9 @@
       <c r="L348" s="16"/>
       <c r="M348" s="16"/>
       <c r="N348" s="17"/>
-    </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O348" s="17"/>
+    </row>
+    <row r="349" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A349" s="13"/>
       <c r="B349" s="14"/>
       <c r="C349" s="14"/>
@@ -8695,8 +9116,9 @@
       <c r="L349" s="16"/>
       <c r="M349" s="16"/>
       <c r="N349" s="17"/>
-    </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O349" s="17"/>
+    </row>
+    <row r="350" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A350" s="13"/>
       <c r="B350" s="14"/>
       <c r="C350" s="14"/>
@@ -8717,8 +9139,9 @@
       <c r="L350" s="16"/>
       <c r="M350" s="16"/>
       <c r="N350" s="17"/>
-    </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O350" s="17"/>
+    </row>
+    <row r="351" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A351" s="13"/>
       <c r="B351" s="14"/>
       <c r="C351" s="14"/>
@@ -8739,8 +9162,9 @@
       <c r="L351" s="16"/>
       <c r="M351" s="16"/>
       <c r="N351" s="17"/>
-    </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O351" s="17"/>
+    </row>
+    <row r="352" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A352" s="13"/>
       <c r="B352" s="14"/>
       <c r="C352" s="14"/>
@@ -8761,8 +9185,9 @@
       <c r="L352" s="16"/>
       <c r="M352" s="16"/>
       <c r="N352" s="17"/>
-    </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O352" s="17"/>
+    </row>
+    <row r="353" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A353" s="13"/>
       <c r="B353" s="14"/>
       <c r="C353" s="14"/>
@@ -8783,8 +9208,9 @@
       <c r="L353" s="16"/>
       <c r="M353" s="16"/>
       <c r="N353" s="17"/>
-    </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O353" s="17"/>
+    </row>
+    <row r="354" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A354" s="13"/>
       <c r="B354" s="14"/>
       <c r="C354" s="14"/>
@@ -8805,8 +9231,9 @@
       <c r="L354" s="16"/>
       <c r="M354" s="16"/>
       <c r="N354" s="17"/>
-    </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O354" s="17"/>
+    </row>
+    <row r="355" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A355" s="13"/>
       <c r="B355" s="14"/>
       <c r="C355" s="14"/>
@@ -8827,8 +9254,9 @@
       <c r="L355" s="16"/>
       <c r="M355" s="16"/>
       <c r="N355" s="17"/>
-    </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O355" s="17"/>
+    </row>
+    <row r="356" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A356" s="13"/>
       <c r="B356" s="14"/>
       <c r="C356" s="14"/>
@@ -8849,8 +9277,9 @@
       <c r="L356" s="16"/>
       <c r="M356" s="16"/>
       <c r="N356" s="17"/>
-    </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O356" s="17"/>
+    </row>
+    <row r="357" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A357" s="13"/>
       <c r="B357" s="14"/>
       <c r="C357" s="14"/>
@@ -8871,8 +9300,9 @@
       <c r="L357" s="16"/>
       <c r="M357" s="16"/>
       <c r="N357" s="17"/>
-    </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O357" s="17"/>
+    </row>
+    <row r="358" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A358" s="13"/>
       <c r="B358" s="14"/>
       <c r="C358" s="14"/>
@@ -8893,8 +9323,9 @@
       <c r="L358" s="16"/>
       <c r="M358" s="16"/>
       <c r="N358" s="17"/>
-    </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O358" s="17"/>
+    </row>
+    <row r="359" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A359" s="13"/>
       <c r="B359" s="14"/>
       <c r="C359" s="14"/>
@@ -8915,8 +9346,9 @@
       <c r="L359" s="16"/>
       <c r="M359" s="16"/>
       <c r="N359" s="17"/>
-    </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O359" s="17"/>
+    </row>
+    <row r="360" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A360" s="13"/>
       <c r="B360" s="14"/>
       <c r="C360" s="14"/>
@@ -8937,8 +9369,9 @@
       <c r="L360" s="16"/>
       <c r="M360" s="16"/>
       <c r="N360" s="17"/>
-    </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O360" s="17"/>
+    </row>
+    <row r="361" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A361" s="13"/>
       <c r="B361" s="14"/>
       <c r="C361" s="14"/>
@@ -8959,8 +9392,9 @@
       <c r="L361" s="16"/>
       <c r="M361" s="16"/>
       <c r="N361" s="17"/>
-    </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O361" s="17"/>
+    </row>
+    <row r="362" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A362" s="13"/>
       <c r="B362" s="14"/>
       <c r="C362" s="14"/>
@@ -8981,8 +9415,9 @@
       <c r="L362" s="16"/>
       <c r="M362" s="16"/>
       <c r="N362" s="17"/>
-    </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O362" s="17"/>
+    </row>
+    <row r="363" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A363" s="13"/>
       <c r="B363" s="14"/>
       <c r="C363" s="14"/>
@@ -9003,8 +9438,9 @@
       <c r="L363" s="16"/>
       <c r="M363" s="16"/>
       <c r="N363" s="17"/>
-    </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O363" s="17"/>
+    </row>
+    <row r="364" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A364" s="13"/>
       <c r="B364" s="14"/>
       <c r="C364" s="14"/>
@@ -9025,8 +9461,9 @@
       <c r="L364" s="16"/>
       <c r="M364" s="16"/>
       <c r="N364" s="17"/>
-    </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O364" s="17"/>
+    </row>
+    <row r="365" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A365" s="13"/>
       <c r="B365" s="14"/>
       <c r="C365" s="14"/>
@@ -9047,8 +9484,9 @@
       <c r="L365" s="16"/>
       <c r="M365" s="16"/>
       <c r="N365" s="17"/>
-    </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O365" s="17"/>
+    </row>
+    <row r="366" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A366" s="13"/>
       <c r="B366" s="14"/>
       <c r="C366" s="14"/>
@@ -9069,8 +9507,9 @@
       <c r="L366" s="16"/>
       <c r="M366" s="16"/>
       <c r="N366" s="17"/>
-    </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O366" s="17"/>
+    </row>
+    <row r="367" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A367" s="13"/>
       <c r="B367" s="14"/>
       <c r="C367" s="14"/>
@@ -9091,8 +9530,9 @@
       <c r="L367" s="16"/>
       <c r="M367" s="16"/>
       <c r="N367" s="17"/>
-    </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O367" s="17"/>
+    </row>
+    <row r="368" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A368" s="13"/>
       <c r="B368" s="14"/>
       <c r="C368" s="14"/>
@@ -9113,8 +9553,9 @@
       <c r="L368" s="16"/>
       <c r="M368" s="16"/>
       <c r="N368" s="17"/>
-    </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O368" s="17"/>
+    </row>
+    <row r="369" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A369" s="13"/>
       <c r="B369" s="14"/>
       <c r="C369" s="14"/>
@@ -9135,8 +9576,9 @@
       <c r="L369" s="16"/>
       <c r="M369" s="16"/>
       <c r="N369" s="17"/>
-    </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O369" s="17"/>
+    </row>
+    <row r="370" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A370" s="13"/>
       <c r="B370" s="14"/>
       <c r="C370" s="14"/>
@@ -9157,8 +9599,9 @@
       <c r="L370" s="16"/>
       <c r="M370" s="16"/>
       <c r="N370" s="17"/>
-    </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O370" s="17"/>
+    </row>
+    <row r="371" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A371" s="13"/>
       <c r="B371" s="14"/>
       <c r="C371" s="14"/>
@@ -9179,8 +9622,9 @@
       <c r="L371" s="16"/>
       <c r="M371" s="16"/>
       <c r="N371" s="17"/>
-    </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O371" s="17"/>
+    </row>
+    <row r="372" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A372" s="13"/>
       <c r="B372" s="14"/>
       <c r="C372" s="14"/>
@@ -9201,8 +9645,9 @@
       <c r="L372" s="16"/>
       <c r="M372" s="16"/>
       <c r="N372" s="17"/>
-    </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O372" s="17"/>
+    </row>
+    <row r="373" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A373" s="13"/>
       <c r="B373" s="14"/>
       <c r="C373" s="14"/>
@@ -9223,8 +9668,9 @@
       <c r="L373" s="16"/>
       <c r="M373" s="16"/>
       <c r="N373" s="17"/>
-    </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O373" s="17"/>
+    </row>
+    <row r="374" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A374" s="13"/>
       <c r="B374" s="14"/>
       <c r="C374" s="14"/>
@@ -9245,8 +9691,9 @@
       <c r="L374" s="16"/>
       <c r="M374" s="16"/>
       <c r="N374" s="17"/>
-    </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O374" s="17"/>
+    </row>
+    <row r="375" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A375" s="13"/>
       <c r="B375" s="14"/>
       <c r="C375" s="14"/>
@@ -9267,8 +9714,9 @@
       <c r="L375" s="16"/>
       <c r="M375" s="16"/>
       <c r="N375" s="17"/>
-    </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O375" s="17"/>
+    </row>
+    <row r="376" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A376" s="13"/>
       <c r="B376" s="14"/>
       <c r="C376" s="14"/>
@@ -9289,8 +9737,9 @@
       <c r="L376" s="16"/>
       <c r="M376" s="16"/>
       <c r="N376" s="17"/>
-    </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O376" s="17"/>
+    </row>
+    <row r="377" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A377" s="13"/>
       <c r="B377" s="14"/>
       <c r="C377" s="14"/>
@@ -9311,8 +9760,9 @@
       <c r="L377" s="16"/>
       <c r="M377" s="16"/>
       <c r="N377" s="17"/>
-    </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O377" s="17"/>
+    </row>
+    <row r="378" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A378" s="13"/>
       <c r="B378" s="14"/>
       <c r="C378" s="14"/>
@@ -9333,8 +9783,9 @@
       <c r="L378" s="16"/>
       <c r="M378" s="16"/>
       <c r="N378" s="17"/>
-    </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O378" s="17"/>
+    </row>
+    <row r="379" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A379" s="13"/>
       <c r="B379" s="14"/>
       <c r="C379" s="14"/>
@@ -9355,8 +9806,9 @@
       <c r="L379" s="16"/>
       <c r="M379" s="16"/>
       <c r="N379" s="17"/>
-    </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O379" s="17"/>
+    </row>
+    <row r="380" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A380" s="13"/>
       <c r="B380" s="14"/>
       <c r="C380" s="14"/>
@@ -9377,8 +9829,9 @@
       <c r="L380" s="16"/>
       <c r="M380" s="16"/>
       <c r="N380" s="17"/>
-    </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O380" s="17"/>
+    </row>
+    <row r="381" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A381" s="13"/>
       <c r="B381" s="14"/>
       <c r="C381" s="14"/>
@@ -9399,8 +9852,9 @@
       <c r="L381" s="16"/>
       <c r="M381" s="16"/>
       <c r="N381" s="17"/>
-    </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O381" s="17"/>
+    </row>
+    <row r="382" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A382" s="13"/>
       <c r="B382" s="14"/>
       <c r="C382" s="14"/>
@@ -9421,8 +9875,9 @@
       <c r="L382" s="16"/>
       <c r="M382" s="16"/>
       <c r="N382" s="17"/>
-    </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O382" s="17"/>
+    </row>
+    <row r="383" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A383" s="13"/>
       <c r="B383" s="14"/>
       <c r="C383" s="14"/>
@@ -9443,8 +9898,9 @@
       <c r="L383" s="16"/>
       <c r="M383" s="16"/>
       <c r="N383" s="17"/>
-    </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O383" s="17"/>
+    </row>
+    <row r="384" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A384" s="13"/>
       <c r="B384" s="14"/>
       <c r="C384" s="14"/>
@@ -9465,8 +9921,9 @@
       <c r="L384" s="16"/>
       <c r="M384" s="16"/>
       <c r="N384" s="17"/>
-    </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O384" s="17"/>
+    </row>
+    <row r="385" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A385" s="13"/>
       <c r="B385" s="14"/>
       <c r="C385" s="14"/>
@@ -9487,8 +9944,9 @@
       <c r="L385" s="16"/>
       <c r="M385" s="16"/>
       <c r="N385" s="17"/>
-    </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O385" s="17"/>
+    </row>
+    <row r="386" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A386" s="13"/>
       <c r="B386" s="14"/>
       <c r="C386" s="14"/>
@@ -9509,8 +9967,9 @@
       <c r="L386" s="16"/>
       <c r="M386" s="16"/>
       <c r="N386" s="17"/>
-    </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O386" s="17"/>
+    </row>
+    <row r="387" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A387" s="13"/>
       <c r="B387" s="14"/>
       <c r="C387" s="14"/>
@@ -9531,8 +9990,9 @@
       <c r="L387" s="16"/>
       <c r="M387" s="16"/>
       <c r="N387" s="17"/>
-    </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O387" s="17"/>
+    </row>
+    <row r="388" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A388" s="13"/>
       <c r="B388" s="14"/>
       <c r="C388" s="14"/>
@@ -9553,8 +10013,9 @@
       <c r="L388" s="16"/>
       <c r="M388" s="16"/>
       <c r="N388" s="17"/>
-    </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O388" s="17"/>
+    </row>
+    <row r="389" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A389" s="13"/>
       <c r="B389" s="14"/>
       <c r="C389" s="14"/>
@@ -9575,8 +10036,9 @@
       <c r="L389" s="16"/>
       <c r="M389" s="16"/>
       <c r="N389" s="17"/>
-    </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O389" s="17"/>
+    </row>
+    <row r="390" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A390" s="13"/>
       <c r="B390" s="14"/>
       <c r="C390" s="14"/>
@@ -9597,8 +10059,9 @@
       <c r="L390" s="16"/>
       <c r="M390" s="16"/>
       <c r="N390" s="17"/>
-    </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O390" s="17"/>
+    </row>
+    <row r="391" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A391" s="13"/>
       <c r="B391" s="14"/>
       <c r="C391" s="14"/>
@@ -9619,8 +10082,9 @@
       <c r="L391" s="16"/>
       <c r="M391" s="16"/>
       <c r="N391" s="17"/>
-    </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O391" s="17"/>
+    </row>
+    <row r="392" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A392" s="13"/>
       <c r="B392" s="14"/>
       <c r="C392" s="14"/>
@@ -9641,8 +10105,9 @@
       <c r="L392" s="16"/>
       <c r="M392" s="16"/>
       <c r="N392" s="17"/>
-    </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O392" s="17"/>
+    </row>
+    <row r="393" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A393" s="13"/>
       <c r="B393" s="14"/>
       <c r="C393" s="14"/>
@@ -9663,8 +10128,9 @@
       <c r="L393" s="16"/>
       <c r="M393" s="16"/>
       <c r="N393" s="17"/>
-    </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O393" s="17"/>
+    </row>
+    <row r="394" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A394" s="13"/>
       <c r="B394" s="14"/>
       <c r="C394" s="14"/>
@@ -9685,8 +10151,9 @@
       <c r="L394" s="16"/>
       <c r="M394" s="16"/>
       <c r="N394" s="17"/>
-    </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O394" s="17"/>
+    </row>
+    <row r="395" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A395" s="13"/>
       <c r="B395" s="14"/>
       <c r="C395" s="14"/>
@@ -9707,8 +10174,9 @@
       <c r="L395" s="16"/>
       <c r="M395" s="16"/>
       <c r="N395" s="17"/>
-    </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O395" s="17"/>
+    </row>
+    <row r="396" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A396" s="13"/>
       <c r="B396" s="14"/>
       <c r="C396" s="14"/>
@@ -9729,8 +10197,9 @@
       <c r="L396" s="16"/>
       <c r="M396" s="16"/>
       <c r="N396" s="17"/>
-    </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O396" s="17"/>
+    </row>
+    <row r="397" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A397" s="13"/>
       <c r="B397" s="14"/>
       <c r="C397" s="14"/>
@@ -9751,8 +10220,9 @@
       <c r="L397" s="16"/>
       <c r="M397" s="16"/>
       <c r="N397" s="17"/>
-    </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O397" s="17"/>
+    </row>
+    <row r="398" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A398" s="13"/>
       <c r="B398" s="14"/>
       <c r="C398" s="14"/>
@@ -9773,8 +10243,9 @@
       <c r="L398" s="16"/>
       <c r="M398" s="16"/>
       <c r="N398" s="17"/>
-    </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O398" s="17"/>
+    </row>
+    <row r="399" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A399" s="13"/>
       <c r="B399" s="14"/>
       <c r="C399" s="14"/>
@@ -9795,8 +10266,9 @@
       <c r="L399" s="16"/>
       <c r="M399" s="16"/>
       <c r="N399" s="17"/>
-    </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O399" s="17"/>
+    </row>
+    <row r="400" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A400" s="13"/>
       <c r="B400" s="14"/>
       <c r="C400" s="14"/>
@@ -9817,8 +10289,9 @@
       <c r="L400" s="16"/>
       <c r="M400" s="16"/>
       <c r="N400" s="17"/>
-    </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O400" s="17"/>
+    </row>
+    <row r="401" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A401" s="13"/>
       <c r="B401" s="14"/>
       <c r="C401" s="14"/>
@@ -9839,6 +10312,7 @@
       <c r="L401" s="16"/>
       <c r="M401" s="16"/>
       <c r="N401" s="17"/>
+      <c r="O401" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEA09D2-8F76-4260-85EB-15D405D9681D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345CAF8B-1D53-4456-AB72-545FE322BD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -240,6 +240,9 @@
   <si>
     <t>Steps</t>
   </si>
+  <si>
+    <t>It was just regular day.</t>
+  </si>
 </sst>
 </file>
 
@@ -418,12 +421,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -908,74 +911,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>12618117</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:15" ht="42" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
@@ -1069,7 +1072,7 @@
       <c r="N6" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="O6" s="21">
+      <c r="O6" s="18">
         <v>9900</v>
       </c>
     </row>
@@ -1368,27 +1371,53 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="8">
+        <v>46253</v>
+      </c>
+      <c r="B13" s="14">
+        <v>270</v>
+      </c>
+      <c r="C13" s="14">
+        <v>40</v>
+      </c>
+      <c r="D13" s="14">
+        <v>50</v>
+      </c>
+      <c r="E13" s="14">
+        <v>20</v>
+      </c>
+      <c r="F13" s="14">
+        <v>420</v>
+      </c>
+      <c r="G13" s="14">
+        <v>7</v>
+      </c>
+      <c r="H13" s="14">
+        <v>300</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="O13" s="17">
+        <v>12903</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="13"/>

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345CAF8B-1D53-4456-AB72-545FE322BD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFB61B6-74DA-456B-B196-1D107E809489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,12 @@
   </si>
   <si>
     <t>It was just regular day.</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Invested time in learning new concepts. Practised leetcode.</t>
   </si>
 </sst>
 </file>
@@ -1419,51 +1425,101 @@
         <v>12903</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+    <row r="14" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="A14" s="8">
+        <v>46254</v>
+      </c>
+      <c r="B14" s="14">
+        <v>270</v>
+      </c>
+      <c r="C14" s="14">
+        <v>50</v>
+      </c>
+      <c r="D14" s="14">
+        <v>130</v>
+      </c>
+      <c r="E14" s="14">
+        <v>110</v>
+      </c>
+      <c r="F14" s="14">
+        <v>360</v>
+      </c>
+      <c r="G14" s="14">
+        <v>6</v>
+      </c>
+      <c r="H14" s="14">
+        <v>250</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="O14" s="17">
+        <v>12016</v>
+      </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B15" s="14">
+        <v>250</v>
+      </c>
+      <c r="C15" s="14">
+        <v>50</v>
+      </c>
+      <c r="D15" s="14">
+        <v>60</v>
+      </c>
+      <c r="E15" s="14">
+        <v>30</v>
+      </c>
+      <c r="F15" s="14">
+        <v>360</v>
+      </c>
+      <c r="G15" s="14">
+        <v>6</v>
+      </c>
+      <c r="H15" s="14">
+        <v>300</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
+        <v>390</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>63</v>
+      </c>
       <c r="N15" s="17"/>
-      <c r="O15" s="17"/>
+      <c r="O15" s="17">
+        <v>9693</v>
+      </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="13"/>

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEFB61B6-74DA-456B-B196-1D107E809489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6005DA66-71C9-44AD-B8D6-2D31255AF27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>Invested time in learning new concepts. Practised leetcode.</t>
+  </si>
+  <si>
+    <t>Speaked in front of the class on the topi how's the most influencial person in your life and why?, Also solved 2 leetcode problems</t>
   </si>
 </sst>
 </file>
@@ -1522,73 +1525,147 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="8">
+        <v>46256</v>
+      </c>
+      <c r="B16" s="14">
+        <v>300</v>
+      </c>
+      <c r="C16" s="14">
+        <v>10</v>
+      </c>
+      <c r="D16" s="14">
+        <v>20</v>
+      </c>
+      <c r="E16" s="14">
+        <v>25</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>400</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>755</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
+        <v>685</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
+      <c r="O16" s="17">
+        <v>107</v>
+      </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="8">
+        <v>46257</v>
+      </c>
+      <c r="B17" s="14">
+        <v>300</v>
+      </c>
+      <c r="C17" s="14">
+        <v>10</v>
+      </c>
+      <c r="D17" s="14">
+        <v>20</v>
+      </c>
+      <c r="E17" s="14">
+        <v>0</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>500</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
+        <v>610</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="O17" s="17">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="8">
+        <v>46258</v>
+      </c>
+      <c r="B18" s="14">
+        <v>250</v>
+      </c>
+      <c r="C18" s="14">
+        <v>45</v>
+      </c>
+      <c r="D18" s="14">
+        <v>150</v>
+      </c>
+      <c r="E18" s="14">
+        <v>80</v>
+      </c>
+      <c r="F18" s="14">
+        <v>240</v>
+      </c>
+      <c r="G18" s="14">
+        <v>4</v>
+      </c>
+      <c r="H18" s="14">
+        <v>300</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1065</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
+        <v>375</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="O18" s="17">
+        <v>6632</v>
+      </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="13"/>

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6005DA66-71C9-44AD-B8D6-2D31255AF27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D68788E-B96B-45CB-ADC7-5D2A0BE15F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Speaked in front of the class on the topi how's the most influencial person in your life and why?, Also solved 2 leetcode problems</t>
+  </si>
+  <si>
+    <t>Solved some leetcode problem. Keep the stream +1 everyday you can do it.</t>
   </si>
 </sst>
 </file>
@@ -1667,28 +1670,54 @@
         <v>6632</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+    <row r="19" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="8">
+        <v>46259</v>
+      </c>
+      <c r="B19" s="14">
+        <v>250</v>
+      </c>
+      <c r="C19" s="14">
+        <v>45</v>
+      </c>
+      <c r="D19" s="14">
+        <v>110</v>
+      </c>
+      <c r="E19" s="14">
+        <v>90</v>
+      </c>
+      <c r="F19" s="14">
+        <v>300</v>
+      </c>
+      <c r="G19" s="14">
+        <v>5</v>
+      </c>
+      <c r="H19" s="14">
+        <v>300</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1095</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
-      <c r="O19" s="17"/>
+        <v>345</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="O19" s="17">
+        <v>10243</v>
+      </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="13"/>

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D68788E-B96B-45CB-ADC7-5D2A0BE15F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4DF0B9-3E20-413E-AE9D-F2BC3FAACD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,12 @@
   </si>
   <si>
     <t>Solved some leetcode problem. Keep the stream +1 everyday you can do it.</t>
+  </si>
+  <si>
+    <t>Nil</t>
+  </si>
+  <si>
+    <t>Stressed</t>
   </si>
 </sst>
 </file>
@@ -1720,14 +1726,30 @@
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
+      <c r="A20" s="8">
+        <v>46260</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>73</v>
+      </c>
       <c r="I20" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1740,17 +1762,35 @@
       <c r="L20" s="16"/>
       <c r="M20" s="16"/>
       <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
+      <c r="O20" s="17">
+        <v>8649</v>
+      </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
+      <c r="A21" s="8">
+        <v>46261</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>73</v>
+      </c>
       <c r="I21" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1763,17 +1803,35 @@
       <c r="L21" s="16"/>
       <c r="M21" s="16"/>
       <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
+      <c r="O21" s="17">
+        <v>3129</v>
+      </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
+      <c r="A22" s="8">
+        <v>46262</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>73</v>
+      </c>
       <c r="I22" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1786,17 +1844,35 @@
       <c r="L22" s="16"/>
       <c r="M22" s="16"/>
       <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
+      <c r="O22" s="17">
+        <v>3902</v>
+      </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
+      <c r="A23" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>73</v>
+      </c>
       <c r="I23" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1809,17 +1885,35 @@
       <c r="L23" s="16"/>
       <c r="M23" s="16"/>
       <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
+      <c r="O23" s="17">
+        <v>804</v>
+      </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="A24" s="8">
+        <v>46264</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>73</v>
+      </c>
       <c r="I24" s="15" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1832,30 +1926,56 @@
       <c r="L24" s="16"/>
       <c r="M24" s="16"/>
       <c r="N24" s="17"/>
-      <c r="O24" s="17"/>
+      <c r="O24" s="17">
+        <v>3091</v>
+      </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B25" s="14">
+        <v>200</v>
+      </c>
+      <c r="C25" s="14">
+        <v>45</v>
+      </c>
+      <c r="D25" s="14">
+        <v>130</v>
+      </c>
+      <c r="E25" s="14">
+        <v>70</v>
+      </c>
+      <c r="F25" s="14">
+        <v>50</v>
+      </c>
+      <c r="G25" s="14">
+        <v>1</v>
+      </c>
+      <c r="H25" s="14">
+        <v>300</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>795</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
+        <v>645</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>63</v>
+      </c>
       <c r="N25" s="17"/>
-      <c r="O25" s="17"/>
+      <c r="O25" s="17">
+        <v>10075</v>
+      </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="13"/>

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4DF0B9-3E20-413E-AE9D-F2BC3FAACD74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC5948A-792E-45AD-B96E-E4852CDA4AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1978,53 +1978,103 @@
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B26" s="14">
+        <v>230</v>
+      </c>
+      <c r="C26" s="14">
+        <v>45</v>
+      </c>
+      <c r="D26" s="14">
+        <v>40</v>
+      </c>
+      <c r="E26" s="14">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
+        <v>250</v>
+      </c>
+      <c r="G26" s="14">
+        <v>5</v>
+      </c>
+      <c r="H26" s="14">
+        <v>350</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>915</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
+        <v>525</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>63</v>
+      </c>
       <c r="N26" s="17"/>
-      <c r="O26" s="17"/>
+      <c r="O26" s="17">
+        <v>7465</v>
+      </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B27" s="14">
+        <v>200</v>
+      </c>
+      <c r="C27" s="14">
+        <v>45</v>
+      </c>
+      <c r="D27" s="14">
+        <v>0</v>
+      </c>
+      <c r="E27" s="14">
+        <v>30</v>
+      </c>
+      <c r="F27" s="14">
+        <v>250</v>
+      </c>
+      <c r="G27" s="14">
+        <v>5</v>
+      </c>
+      <c r="H27" s="14">
+        <v>300</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>825</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
+        <v>615</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="N27" s="17"/>
-      <c r="O27" s="17"/>
+      <c r="O27" s="17">
+        <v>7708</v>
+      </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A28" s="13"/>
+      <c r="A28" s="8">
+        <v>46268</v>
+      </c>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>

--- a/12618117.xlsx
+++ b/12618117.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krish\Desktop\MCA_SEM1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC5948A-792E-45AD-B96E-E4852CDA4AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CA99BE-B98F-4165-BD0C-343AF0AA35E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>Stressed</t>
+  </si>
+  <si>
+    <t>I had cold, cough and sore throat</t>
   </si>
 </sst>
 </file>
@@ -2071,53 +2074,103 @@
         <v>7708</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="8">
         <v>46268</v>
       </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="B28" s="14">
+        <v>200</v>
+      </c>
+      <c r="C28" s="14">
+        <v>30</v>
+      </c>
+      <c r="D28" s="14">
+        <v>30</v>
+      </c>
+      <c r="E28" s="14">
+        <v>30</v>
+      </c>
+      <c r="F28" s="14">
+        <v>0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>0</v>
+      </c>
+      <c r="H28" s="14">
+        <v>350</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>640</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
-      <c r="O28" s="17"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="O28" s="17">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="A29" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B29" s="14">
+        <v>220</v>
+      </c>
+      <c r="C29" s="14">
+        <v>30</v>
+      </c>
+      <c r="D29" s="14">
+        <v>0</v>
+      </c>
+      <c r="E29" s="14">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>150</v>
+      </c>
+      <c r="G29" s="14">
+        <v>3</v>
+      </c>
+      <c r="H29" s="14">
+        <v>400</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
-      <c r="O29" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="O29" s="17">
+        <v>6663</v>
+      </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="13"/>
